--- a/outputs/54667.xlsx
+++ b/outputs/54667.xlsx
@@ -737,20 +737,20 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="92">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -762,15 +762,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -802,35 +802,35 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -838,83 +838,87 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="12" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="12" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="12" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="12" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="12" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="12" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="3" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="3" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="8" borderId="4" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="8" borderId="5" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="8" borderId="6" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="8" borderId="6" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="8" borderId="6" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="8" borderId="7" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="8" borderId="4" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="5" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="8" borderId="6" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="6" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="8" borderId="6" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="8" borderId="7" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -942,51 +946,51 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="11" borderId="11" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="11" borderId="12" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="12" borderId="13" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="12" borderId="11" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="12" borderId="11" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="12" borderId="14" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="12" borderId="15" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="11" borderId="13" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="11" borderId="16" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="12" borderId="13" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="12" borderId="17" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="12" borderId="18" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="4" fillId="11" borderId="11" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="11" borderId="12" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="12" borderId="13" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="12" borderId="11" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="12" borderId="11" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="12" borderId="14" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="12" borderId="15" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="11" borderId="13" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="11" borderId="16" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="12" borderId="13" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="12" borderId="17" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="12" borderId="18" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1030,67 +1034,67 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="11" borderId="23" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="11" borderId="24" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="12" borderId="25" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="12" borderId="23" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="12" borderId="26" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="12" borderId="27" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="13" borderId="28" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="13" borderId="29" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="4" fillId="11" borderId="23" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="11" borderId="24" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="12" borderId="25" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="12" borderId="23" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="12" borderId="26" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="12" borderId="27" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="13" borderId="28" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="13" borderId="29" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1098,7 +1102,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1413,10 +1417,10 @@
       </c>
       <c r="F3" s="12" t="n">
         <f aca="true">IF(OR(B3="PRG/FLY",B3="PRG/TVL",B3="FLY1",B3="TVL1",B3="PRG/FLY-CO",B3="PRG/TVL-CO",B3="FLY1-CO",B3="TVL1-CO"),IF(IFERROR(1/(1/F3),"")="",TODAY()+VLOOKUP(C3,DATA!$A:$E,4,0),F3),"")</f>
-        <v>46270.3645833333</v>
+        <v>46271.3645833333</v>
       </c>
       <c r="G3" s="4" t="n">
-        <f aca="false">IF(E3=D3,M3,IFERROR(VLOOKUP(C3,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D3=E3,M3,IFERROR(VLOOKUP(C3,DATA!$A:$E,5,0),""))</f>
         <v>0.0520833333333333</v>
       </c>
       <c r="M3" s="4" t="n">
@@ -1444,7 +1448,7 @@
         <v/>
       </c>
       <c r="G4" s="4" t="n">
-        <f aca="false">IF(E4=D4,M4,IFERROR(VLOOKUP(C4,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D4=E4,M4,IFERROR(VLOOKUP(C4,DATA!$A:$E,5,0),""))</f>
         <v>0.0381944444444445</v>
       </c>
       <c r="M4" s="4" t="n">
@@ -1471,7 +1475,7 @@
         <v/>
       </c>
       <c r="G5" s="15" t="n">
-        <f aca="false">IF(E5=D5,M5,IFERROR(VLOOKUP(C5,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D5=E5,M5,IFERROR(VLOOKUP(C5,DATA!$A:$E,5,0),""))</f>
         <v>0.05625</v>
       </c>
       <c r="M5" s="15" t="n">
@@ -1495,7 +1499,7 @@
         <v/>
       </c>
       <c r="G6" s="4" t="n">
-        <f aca="false">IF(E6=D6,M6,IFERROR(VLOOKUP(C6,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D6=E6,M6,IFERROR(VLOOKUP(C6,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -1516,7 +1520,7 @@
         <v/>
       </c>
       <c r="G7" s="4" t="n">
-        <f aca="false">IF(E7=D7,M7,IFERROR(VLOOKUP(C7,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D7=E7,M7,IFERROR(VLOOKUP(C7,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -1537,7 +1541,7 @@
         <v/>
       </c>
       <c r="G8" s="4" t="n">
-        <f aca="false">IF(E8=D8,M8,IFERROR(VLOOKUP(C8,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D8=E8,M8,IFERROR(VLOOKUP(C8,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -1558,7 +1562,7 @@
         <v/>
       </c>
       <c r="G9" s="4" t="n">
-        <f aca="false">IF(E9=D9,M9,IFERROR(VLOOKUP(C9,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D9=E9,M9,IFERROR(VLOOKUP(C9,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -1579,7 +1583,7 @@
         <v/>
       </c>
       <c r="G10" s="4" t="n">
-        <f aca="false">IF(E10=D10,M10,IFERROR(VLOOKUP(C10,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D10=E10,M10,IFERROR(VLOOKUP(C10,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -1600,7 +1604,7 @@
         <v/>
       </c>
       <c r="G11" s="4" t="n">
-        <f aca="false">IF(E11=D11,M11,IFERROR(VLOOKUP(C11,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D11=E11,M11,IFERROR(VLOOKUP(C11,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -1621,7 +1625,7 @@
         <v/>
       </c>
       <c r="G12" s="4" t="n">
-        <f aca="false">IF(E12=D12,M12,IFERROR(VLOOKUP(C12,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D12=E12,M12,IFERROR(VLOOKUP(C12,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -1642,7 +1646,7 @@
         <v/>
       </c>
       <c r="G13" s="4" t="n">
-        <f aca="false">IF(E13=D13,M13,IFERROR(VLOOKUP(C13,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D13=E13,M13,IFERROR(VLOOKUP(C13,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -1663,7 +1667,7 @@
         <v/>
       </c>
       <c r="G14" s="4" t="n">
-        <f aca="false">IF(E14=D14,M14,IFERROR(VLOOKUP(C14,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D14=E14,M14,IFERROR(VLOOKUP(C14,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -1684,7 +1688,7 @@
         <v/>
       </c>
       <c r="G15" s="4" t="n">
-        <f aca="false">IF(E15=D15,M15,IFERROR(VLOOKUP(C15,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D15=E15,M15,IFERROR(VLOOKUP(C15,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -1705,7 +1709,7 @@
         <v/>
       </c>
       <c r="G16" s="4" t="n">
-        <f aca="false">IF(E16=D16,M16,IFERROR(VLOOKUP(C16,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D16=E16,M16,IFERROR(VLOOKUP(C16,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -1726,7 +1730,7 @@
         <v/>
       </c>
       <c r="G17" s="4" t="n">
-        <f aca="false">IF(E17=D17,M17,IFERROR(VLOOKUP(C17,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D17=E17,M17,IFERROR(VLOOKUP(C17,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -1747,7 +1751,7 @@
         <v/>
       </c>
       <c r="G18" s="4" t="n">
-        <f aca="false">IF(E18=D18,M18,IFERROR(VLOOKUP(C18,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D18=E18,M18,IFERROR(VLOOKUP(C18,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -1768,7 +1772,7 @@
         <v/>
       </c>
       <c r="G19" s="4" t="n">
-        <f aca="false">IF(E19=D19,M19,IFERROR(VLOOKUP(C19,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D19=E19,M19,IFERROR(VLOOKUP(C19,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -1789,7 +1793,7 @@
         <v/>
       </c>
       <c r="G20" s="4" t="n">
-        <f aca="false">IF(E20=D20,M20,IFERROR(VLOOKUP(C20,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D20=E20,M20,IFERROR(VLOOKUP(C20,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -1810,7 +1814,7 @@
         <v/>
       </c>
       <c r="G21" s="4" t="n">
-        <f aca="false">IF(E21=D21,M21,IFERROR(VLOOKUP(C21,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D21=E21,M21,IFERROR(VLOOKUP(C21,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -1831,7 +1835,7 @@
         <v/>
       </c>
       <c r="G22" s="4" t="n">
-        <f aca="false">IF(E22=D22,M22,IFERROR(VLOOKUP(C22,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D22=E22,M22,IFERROR(VLOOKUP(C22,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -1852,7 +1856,7 @@
         <v/>
       </c>
       <c r="G23" s="4" t="n">
-        <f aca="false">IF(E23=D23,M23,IFERROR(VLOOKUP(C23,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D23=E23,M23,IFERROR(VLOOKUP(C23,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -1873,7 +1877,7 @@
         <v/>
       </c>
       <c r="G24" s="4" t="n">
-        <f aca="false">IF(E24=D24,M24,IFERROR(VLOOKUP(C24,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D24=E24,M24,IFERROR(VLOOKUP(C24,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -1894,7 +1898,7 @@
         <v/>
       </c>
       <c r="G25" s="4" t="n">
-        <f aca="false">IF(E25=D25,M25,IFERROR(VLOOKUP(C25,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D25=E25,M25,IFERROR(VLOOKUP(C25,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -1915,7 +1919,7 @@
         <v/>
       </c>
       <c r="G26" s="4" t="n">
-        <f aca="false">IF(E26=D26,M26,IFERROR(VLOOKUP(C26,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D26=E26,M26,IFERROR(VLOOKUP(C26,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -1936,7 +1940,7 @@
         <v/>
       </c>
       <c r="G27" s="4" t="n">
-        <f aca="false">IF(E27=D27,M27,IFERROR(VLOOKUP(C27,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D27=E27,M27,IFERROR(VLOOKUP(C27,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -1957,7 +1961,7 @@
         <v/>
       </c>
       <c r="G28" s="4" t="n">
-        <f aca="false">IF(E28=D28,M28,IFERROR(VLOOKUP(C28,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D28=E28,M28,IFERROR(VLOOKUP(C28,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -1978,7 +1982,7 @@
         <v/>
       </c>
       <c r="G29" s="4" t="n">
-        <f aca="false">IF(E29=D29,M29,IFERROR(VLOOKUP(C29,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D29=E29,M29,IFERROR(VLOOKUP(C29,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -1999,7 +2003,7 @@
         <v/>
       </c>
       <c r="G30" s="4" t="n">
-        <f aca="false">IF(E30=D30,M30,IFERROR(VLOOKUP(C30,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D30=E30,M30,IFERROR(VLOOKUP(C30,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2020,7 +2024,7 @@
         <v/>
       </c>
       <c r="G31" s="4" t="n">
-        <f aca="false">IF(E31=D31,M31,IFERROR(VLOOKUP(C31,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D31=E31,M31,IFERROR(VLOOKUP(C31,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2041,7 +2045,7 @@
         <v/>
       </c>
       <c r="G32" s="4" t="n">
-        <f aca="false">IF(E32=D32,M32,IFERROR(VLOOKUP(C32,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D32=E32,M32,IFERROR(VLOOKUP(C32,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2062,7 +2066,7 @@
         <v/>
       </c>
       <c r="G33" s="4" t="n">
-        <f aca="false">IF(E33=D33,M33,IFERROR(VLOOKUP(C33,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D33=E33,M33,IFERROR(VLOOKUP(C33,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2083,7 +2087,7 @@
         <v/>
       </c>
       <c r="G34" s="4" t="n">
-        <f aca="false">IF(E34=D34,M34,IFERROR(VLOOKUP(C34,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D34=E34,M34,IFERROR(VLOOKUP(C34,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2104,7 +2108,7 @@
         <v/>
       </c>
       <c r="G35" s="4" t="n">
-        <f aca="false">IF(E35=D35,M35,IFERROR(VLOOKUP(C35,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D35=E35,M35,IFERROR(VLOOKUP(C35,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2125,7 +2129,7 @@
         <v/>
       </c>
       <c r="G36" s="4" t="n">
-        <f aca="false">IF(E36=D36,M36,IFERROR(VLOOKUP(C36,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D36=E36,M36,IFERROR(VLOOKUP(C36,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2146,7 +2150,7 @@
         <v/>
       </c>
       <c r="G37" s="4" t="n">
-        <f aca="false">IF(E37=D37,M37,IFERROR(VLOOKUP(C37,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D37=E37,M37,IFERROR(VLOOKUP(C37,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2167,7 +2171,7 @@
         <v/>
       </c>
       <c r="G38" s="4" t="n">
-        <f aca="false">IF(E38=D38,M38,IFERROR(VLOOKUP(C38,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D38=E38,M38,IFERROR(VLOOKUP(C38,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2188,7 +2192,7 @@
         <v/>
       </c>
       <c r="G39" s="4" t="n">
-        <f aca="false">IF(E39=D39,M39,IFERROR(VLOOKUP(C39,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D39=E39,M39,IFERROR(VLOOKUP(C39,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2209,7 +2213,7 @@
         <v/>
       </c>
       <c r="G40" s="4" t="n">
-        <f aca="false">IF(E40=D40,M40,IFERROR(VLOOKUP(C40,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D40=E40,M40,IFERROR(VLOOKUP(C40,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2230,7 +2234,7 @@
         <v/>
       </c>
       <c r="G41" s="4" t="n">
-        <f aca="false">IF(E41=D41,M41,IFERROR(VLOOKUP(C41,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D41=E41,M41,IFERROR(VLOOKUP(C41,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2251,7 +2255,7 @@
         <v/>
       </c>
       <c r="G42" s="4" t="n">
-        <f aca="false">IF(E42=D42,M42,IFERROR(VLOOKUP(C42,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D42=E42,M42,IFERROR(VLOOKUP(C42,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2272,7 +2276,7 @@
         <v/>
       </c>
       <c r="G43" s="4" t="n">
-        <f aca="false">IF(E43=D43,M43,IFERROR(VLOOKUP(C43,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D43=E43,M43,IFERROR(VLOOKUP(C43,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2293,7 +2297,7 @@
         <v/>
       </c>
       <c r="G44" s="4" t="n">
-        <f aca="false">IF(E44=D44,M44,IFERROR(VLOOKUP(C44,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D44=E44,M44,IFERROR(VLOOKUP(C44,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2314,7 +2318,7 @@
         <v/>
       </c>
       <c r="G45" s="4" t="n">
-        <f aca="false">IF(E45=D45,M45,IFERROR(VLOOKUP(C45,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D45=E45,M45,IFERROR(VLOOKUP(C45,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2335,7 +2339,7 @@
         <v/>
       </c>
       <c r="G46" s="4" t="n">
-        <f aca="false">IF(E46=D46,M46,IFERROR(VLOOKUP(C46,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D46=E46,M46,IFERROR(VLOOKUP(C46,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2356,7 +2360,7 @@
         <v/>
       </c>
       <c r="G47" s="4" t="n">
-        <f aca="false">IF(E47=D47,M47,IFERROR(VLOOKUP(C47,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D47=E47,M47,IFERROR(VLOOKUP(C47,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2377,7 +2381,7 @@
         <v/>
       </c>
       <c r="G48" s="4" t="n">
-        <f aca="false">IF(E48=D48,M48,IFERROR(VLOOKUP(C48,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D48=E48,M48,IFERROR(VLOOKUP(C48,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2398,7 +2402,7 @@
         <v/>
       </c>
       <c r="G49" s="4" t="n">
-        <f aca="false">IF(E49=D49,M49,IFERROR(VLOOKUP(C49,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D49=E49,M49,IFERROR(VLOOKUP(C49,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2419,7 +2423,7 @@
         <v/>
       </c>
       <c r="G50" s="4" t="n">
-        <f aca="false">IF(E50=D50,M50,IFERROR(VLOOKUP(C50,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D50=E50,M50,IFERROR(VLOOKUP(C50,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2440,7 +2444,7 @@
         <v/>
       </c>
       <c r="G51" s="4" t="n">
-        <f aca="false">IF(E51=D51,M51,IFERROR(VLOOKUP(C51,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D51=E51,M51,IFERROR(VLOOKUP(C51,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2461,7 +2465,7 @@
         <v/>
       </c>
       <c r="G52" s="4" t="n">
-        <f aca="false">IF(E52=D52,M52,IFERROR(VLOOKUP(C52,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D52=E52,M52,IFERROR(VLOOKUP(C52,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2482,7 +2486,7 @@
         <v/>
       </c>
       <c r="G53" s="4" t="n">
-        <f aca="false">IF(E53=D53,M53,IFERROR(VLOOKUP(C53,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D53=E53,M53,IFERROR(VLOOKUP(C53,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2503,7 +2507,7 @@
         <v/>
       </c>
       <c r="G54" s="4" t="n">
-        <f aca="false">IF(E54=D54,M54,IFERROR(VLOOKUP(C54,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D54=E54,M54,IFERROR(VLOOKUP(C54,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2524,7 +2528,7 @@
         <v/>
       </c>
       <c r="G55" s="4" t="n">
-        <f aca="false">IF(E55=D55,M55,IFERROR(VLOOKUP(C55,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D55=E55,M55,IFERROR(VLOOKUP(C55,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2545,7 +2549,7 @@
         <v/>
       </c>
       <c r="G56" s="4" t="n">
-        <f aca="false">IF(E56=D56,M56,IFERROR(VLOOKUP(C56,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D56=E56,M56,IFERROR(VLOOKUP(C56,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2566,7 +2570,7 @@
         <v/>
       </c>
       <c r="G57" s="4" t="n">
-        <f aca="false">IF(E57=D57,M57,IFERROR(VLOOKUP(C57,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D57=E57,M57,IFERROR(VLOOKUP(C57,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2587,7 +2591,7 @@
         <v/>
       </c>
       <c r="G58" s="4" t="n">
-        <f aca="false">IF(E58=D58,M58,IFERROR(VLOOKUP(C58,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(D58=E58,M58,IFERROR(VLOOKUP(C58,DATA!$A:$E,5,0),""))</f>
         <v>0</v>
       </c>
     </row>
@@ -2913,1681 +2917,1681 @@
   <dimension ref="A1:V71"/>
   <sheetFormatPr defaultColWidth="8.859375" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="8.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="11.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="33" width="11.14"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="10" min="10" style="33" width="12.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="33" width="11.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="12" style="0" width="8.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="33" width="8.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="33" width="11.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="33" width="8.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="33" width="11.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="34" width="11.14"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="10" min="10" style="34" width="12.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="34" width="11.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="12" style="33" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="34"/>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="37"/>
-      <c r="R1" s="37"/>
-      <c r="S1" s="37"/>
-      <c r="T1" s="37"/>
-      <c r="U1" s="37"/>
-      <c r="V1" s="38"/>
+      <c r="A1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="39"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="39"/>
-      <c r="B2" s="40"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="43"/>
-      <c r="O2" s="43"/>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="43"/>
-      <c r="R2" s="43"/>
-      <c r="S2" s="43"/>
-      <c r="T2" s="43"/>
-      <c r="U2" s="43"/>
-      <c r="V2" s="38"/>
+      <c r="A2" s="40"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="45"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="44"/>
+      <c r="S2" s="44"/>
+      <c r="T2" s="44"/>
+      <c r="U2" s="44"/>
+      <c r="V2" s="39"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="45" t="n">
+      <c r="A3" s="46" t="n">
         <v>1000</v>
       </c>
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="47" t="s">
+      <c r="C3" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="48" t="n">
+      <c r="D3" s="49" t="n">
         <v>0.260416666666667</v>
       </c>
-      <c r="E3" s="48" t="n">
+      <c r="E3" s="49" t="n">
         <v>0.0659722222222222</v>
       </c>
-      <c r="F3" s="48"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="53"/>
-      <c r="M3" s="53"/>
-      <c r="N3" s="54"/>
-      <c r="O3" s="53"/>
-      <c r="P3" s="54"/>
-      <c r="Q3" s="54"/>
-      <c r="R3" s="54"/>
-      <c r="S3" s="55"/>
-      <c r="T3" s="56"/>
-      <c r="U3" s="57"/>
-      <c r="V3" s="38"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="55"/>
+      <c r="O3" s="54"/>
+      <c r="P3" s="55"/>
+      <c r="Q3" s="55"/>
+      <c r="R3" s="55"/>
+      <c r="S3" s="56"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="58"/>
+      <c r="V3" s="39"/>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="45" t="n">
+      <c r="A4" s="46" t="n">
         <v>1001</v>
       </c>
-      <c r="B4" s="46" t="s">
+      <c r="B4" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="47" t="s">
+      <c r="C4" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="48" t="n">
+      <c r="D4" s="49" t="n">
         <v>0.270833333333333</v>
       </c>
-      <c r="E4" s="48" t="n">
+      <c r="E4" s="49" t="n">
         <v>0.0659722222222222</v>
       </c>
-      <c r="F4" s="48"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="59"/>
-      <c r="K4" s="58"/>
-      <c r="L4" s="53"/>
-      <c r="M4" s="53"/>
-      <c r="N4" s="53"/>
-      <c r="O4" s="53"/>
-      <c r="P4" s="53"/>
-      <c r="Q4" s="53"/>
-      <c r="R4" s="53"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="61"/>
-      <c r="U4" s="62"/>
-      <c r="V4" s="38"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="59"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="54"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+      <c r="Q4" s="54"/>
+      <c r="R4" s="54"/>
+      <c r="S4" s="61"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="63"/>
+      <c r="V4" s="39"/>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="45" t="n">
+      <c r="A5" s="46" t="n">
         <v>1002</v>
       </c>
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C5" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="48" t="n">
+      <c r="D5" s="49" t="n">
         <v>0.28125</v>
       </c>
-      <c r="E5" s="48" t="n">
+      <c r="E5" s="49" t="n">
         <v>0.09375</v>
       </c>
-      <c r="F5" s="48"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="58"/>
-      <c r="L5" s="53"/>
-      <c r="M5" s="53"/>
-      <c r="N5" s="53"/>
-      <c r="O5" s="53"/>
-      <c r="P5" s="53"/>
-      <c r="Q5" s="53"/>
-      <c r="R5" s="53"/>
-      <c r="S5" s="60"/>
-      <c r="T5" s="61"/>
-      <c r="U5" s="62"/>
-      <c r="V5" s="38"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="59"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="54"/>
+      <c r="N5" s="54"/>
+      <c r="O5" s="54"/>
+      <c r="P5" s="54"/>
+      <c r="Q5" s="54"/>
+      <c r="R5" s="54"/>
+      <c r="S5" s="61"/>
+      <c r="T5" s="62"/>
+      <c r="U5" s="63"/>
+      <c r="V5" s="39"/>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="45" t="n">
+      <c r="A6" s="46" t="n">
         <v>1003</v>
       </c>
-      <c r="B6" s="46" t="s">
+      <c r="B6" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="C6" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="48" t="n">
+      <c r="D6" s="49" t="n">
         <v>0.291666666666667</v>
       </c>
-      <c r="E6" s="48" t="n">
+      <c r="E6" s="49" t="n">
         <v>0.0833333333333333</v>
       </c>
-      <c r="F6" s="48"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="63"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="59"/>
-      <c r="K6" s="58"/>
-      <c r="L6" s="53"/>
-      <c r="M6" s="53"/>
-      <c r="N6" s="53"/>
-      <c r="O6" s="53"/>
-      <c r="P6" s="53"/>
-      <c r="Q6" s="53"/>
-      <c r="R6" s="53"/>
-      <c r="S6" s="60"/>
-      <c r="T6" s="61"/>
-      <c r="U6" s="62"/>
-      <c r="V6" s="38"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="60"/>
+      <c r="K6" s="59"/>
+      <c r="L6" s="54"/>
+      <c r="M6" s="54"/>
+      <c r="N6" s="54"/>
+      <c r="O6" s="54"/>
+      <c r="P6" s="54"/>
+      <c r="Q6" s="54"/>
+      <c r="R6" s="54"/>
+      <c r="S6" s="61"/>
+      <c r="T6" s="62"/>
+      <c r="U6" s="63"/>
+      <c r="V6" s="39"/>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="45" t="n">
+      <c r="A7" s="46" t="n">
         <v>1004</v>
       </c>
-      <c r="B7" s="46" t="s">
+      <c r="B7" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="48" t="n">
+      <c r="D7" s="49" t="n">
         <v>0.302083333333333</v>
       </c>
-      <c r="E7" s="48" t="n">
+      <c r="E7" s="49" t="n">
         <v>0.09375</v>
       </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="59"/>
-      <c r="K7" s="58"/>
-      <c r="L7" s="53"/>
-      <c r="M7" s="53"/>
-      <c r="N7" s="53"/>
-      <c r="O7" s="53"/>
-      <c r="P7" s="53"/>
-      <c r="Q7" s="53"/>
-      <c r="R7" s="53"/>
-      <c r="S7" s="60"/>
-      <c r="T7" s="61"/>
-      <c r="U7" s="62"/>
-      <c r="V7" s="38"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="50"/>
+      <c r="H7" s="50"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="60"/>
+      <c r="K7" s="59"/>
+      <c r="L7" s="54"/>
+      <c r="M7" s="54"/>
+      <c r="N7" s="54"/>
+      <c r="O7" s="54"/>
+      <c r="P7" s="54"/>
+      <c r="Q7" s="54"/>
+      <c r="R7" s="54"/>
+      <c r="S7" s="61"/>
+      <c r="T7" s="62"/>
+      <c r="U7" s="63"/>
+      <c r="V7" s="39"/>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="45" t="n">
+      <c r="A8" s="46" t="n">
         <v>1005</v>
       </c>
-      <c r="B8" s="46" t="s">
+      <c r="B8" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="47" t="s">
+      <c r="C8" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="48" t="n">
+      <c r="D8" s="49" t="n">
         <v>0.3125</v>
       </c>
-      <c r="E8" s="48" t="n">
+      <c r="E8" s="49" t="n">
         <v>0.0833333333333333</v>
       </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="59"/>
-      <c r="K8" s="58"/>
-      <c r="L8" s="53"/>
-      <c r="M8" s="53"/>
-      <c r="N8" s="53"/>
-      <c r="O8" s="53"/>
-      <c r="P8" s="53"/>
-      <c r="Q8" s="53"/>
-      <c r="R8" s="53"/>
-      <c r="S8" s="60"/>
-      <c r="T8" s="61"/>
-      <c r="U8" s="62"/>
-      <c r="V8" s="38"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="50"/>
+      <c r="H8" s="50"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="59"/>
+      <c r="L8" s="54"/>
+      <c r="M8" s="54"/>
+      <c r="N8" s="54"/>
+      <c r="O8" s="54"/>
+      <c r="P8" s="54"/>
+      <c r="Q8" s="54"/>
+      <c r="R8" s="54"/>
+      <c r="S8" s="61"/>
+      <c r="T8" s="62"/>
+      <c r="U8" s="63"/>
+      <c r="V8" s="39"/>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="45" t="n">
+      <c r="A9" s="46" t="n">
         <v>1006</v>
       </c>
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="47" t="s">
+      <c r="C9" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="48" t="n">
+      <c r="D9" s="49" t="n">
         <v>0.322916666666667</v>
       </c>
-      <c r="E9" s="48" t="n">
+      <c r="E9" s="49" t="n">
         <v>0.0555555555555556</v>
       </c>
-      <c r="F9" s="48"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="58"/>
-      <c r="J9" s="59"/>
-      <c r="K9" s="58"/>
-      <c r="L9" s="53"/>
-      <c r="M9" s="53"/>
-      <c r="N9" s="53"/>
-      <c r="O9" s="53"/>
-      <c r="P9" s="53"/>
-      <c r="Q9" s="53"/>
-      <c r="R9" s="53"/>
-      <c r="S9" s="60"/>
-      <c r="T9" s="61"/>
-      <c r="U9" s="62"/>
-      <c r="V9" s="38"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="50"/>
+      <c r="H9" s="50"/>
+      <c r="I9" s="59"/>
+      <c r="J9" s="60"/>
+      <c r="K9" s="59"/>
+      <c r="L9" s="54"/>
+      <c r="M9" s="54"/>
+      <c r="N9" s="54"/>
+      <c r="O9" s="54"/>
+      <c r="P9" s="54"/>
+      <c r="Q9" s="54"/>
+      <c r="R9" s="54"/>
+      <c r="S9" s="61"/>
+      <c r="T9" s="62"/>
+      <c r="U9" s="63"/>
+      <c r="V9" s="39"/>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="45" t="n">
+      <c r="A10" s="46" t="n">
         <v>1007</v>
       </c>
-      <c r="B10" s="46" t="s">
+      <c r="B10" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="47" t="s">
+      <c r="C10" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="48" t="n">
+      <c r="D10" s="49" t="n">
         <v>0.333333333333333</v>
       </c>
-      <c r="E10" s="48" t="n">
+      <c r="E10" s="49" t="n">
         <v>0.0555555555555556</v>
       </c>
-      <c r="F10" s="48"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="58"/>
-      <c r="J10" s="59"/>
-      <c r="K10" s="58"/>
-      <c r="L10" s="53"/>
-      <c r="M10" s="53"/>
-      <c r="N10" s="53"/>
-      <c r="O10" s="53"/>
-      <c r="P10" s="53"/>
-      <c r="Q10" s="53"/>
-      <c r="R10" s="53"/>
-      <c r="S10" s="60"/>
-      <c r="T10" s="61"/>
-      <c r="U10" s="62"/>
-      <c r="V10" s="38"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="50"/>
+      <c r="H10" s="50"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="60"/>
+      <c r="K10" s="59"/>
+      <c r="L10" s="54"/>
+      <c r="M10" s="54"/>
+      <c r="N10" s="54"/>
+      <c r="O10" s="54"/>
+      <c r="P10" s="54"/>
+      <c r="Q10" s="54"/>
+      <c r="R10" s="54"/>
+      <c r="S10" s="61"/>
+      <c r="T10" s="62"/>
+      <c r="U10" s="63"/>
+      <c r="V10" s="39"/>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="45" t="n">
+      <c r="A11" s="46" t="n">
         <v>1008</v>
       </c>
-      <c r="B11" s="46" t="s">
+      <c r="B11" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="47" t="s">
+      <c r="C11" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="48" t="n">
+      <c r="D11" s="49" t="n">
         <v>0.34375</v>
       </c>
-      <c r="E11" s="48" t="n">
+      <c r="E11" s="49" t="n">
         <v>0.0590277777777778</v>
       </c>
-      <c r="F11" s="48"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="58"/>
-      <c r="J11" s="59"/>
-      <c r="K11" s="58"/>
-      <c r="L11" s="53"/>
-      <c r="M11" s="53"/>
-      <c r="N11" s="53"/>
-      <c r="O11" s="53"/>
-      <c r="P11" s="53"/>
-      <c r="Q11" s="53"/>
-      <c r="R11" s="53"/>
-      <c r="S11" s="60"/>
-      <c r="T11" s="61"/>
-      <c r="U11" s="62"/>
-      <c r="V11" s="38"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="50"/>
+      <c r="H11" s="50"/>
+      <c r="I11" s="59"/>
+      <c r="J11" s="60"/>
+      <c r="K11" s="59"/>
+      <c r="L11" s="54"/>
+      <c r="M11" s="54"/>
+      <c r="N11" s="54"/>
+      <c r="O11" s="54"/>
+      <c r="P11" s="54"/>
+      <c r="Q11" s="54"/>
+      <c r="R11" s="54"/>
+      <c r="S11" s="61"/>
+      <c r="T11" s="62"/>
+      <c r="U11" s="63"/>
+      <c r="V11" s="39"/>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="45" t="n">
+      <c r="A12" s="46" t="n">
         <v>1009</v>
       </c>
-      <c r="B12" s="46" t="s">
+      <c r="B12" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="47" t="s">
+      <c r="C12" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="48" t="n">
+      <c r="D12" s="49" t="n">
         <v>0.354166666666667</v>
       </c>
-      <c r="E12" s="48" t="n">
+      <c r="E12" s="49" t="n">
         <v>0.0590277777777778</v>
       </c>
-      <c r="F12" s="48"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="58"/>
-      <c r="J12" s="59"/>
-      <c r="K12" s="58"/>
-      <c r="L12" s="53"/>
-      <c r="M12" s="53"/>
-      <c r="N12" s="53"/>
-      <c r="O12" s="53"/>
-      <c r="P12" s="53"/>
-      <c r="Q12" s="53"/>
-      <c r="R12" s="53"/>
-      <c r="S12" s="60"/>
-      <c r="T12" s="61"/>
-      <c r="U12" s="62"/>
-      <c r="V12" s="38"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="59"/>
+      <c r="L12" s="54"/>
+      <c r="M12" s="54"/>
+      <c r="N12" s="54"/>
+      <c r="O12" s="54"/>
+      <c r="P12" s="54"/>
+      <c r="Q12" s="54"/>
+      <c r="R12" s="54"/>
+      <c r="S12" s="61"/>
+      <c r="T12" s="62"/>
+      <c r="U12" s="63"/>
+      <c r="V12" s="39"/>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="45" t="n">
+      <c r="A13" s="46" t="n">
         <v>1010</v>
       </c>
-      <c r="B13" s="46" t="s">
+      <c r="B13" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="47" t="s">
+      <c r="C13" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="48" t="n">
+      <c r="D13" s="49" t="n">
         <v>0.364583333333333</v>
       </c>
-      <c r="E13" s="48" t="n">
+      <c r="E13" s="49" t="n">
         <v>0.0520833333333333</v>
       </c>
-      <c r="F13" s="48"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="49"/>
-      <c r="I13" s="58"/>
-      <c r="J13" s="59"/>
-      <c r="K13" s="58"/>
-      <c r="L13" s="53"/>
-      <c r="M13" s="53"/>
-      <c r="N13" s="53"/>
-      <c r="O13" s="53"/>
-      <c r="P13" s="53"/>
-      <c r="Q13" s="53"/>
-      <c r="R13" s="53"/>
-      <c r="S13" s="60"/>
-      <c r="T13" s="61"/>
-      <c r="U13" s="62"/>
-      <c r="V13" s="38"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="50"/>
+      <c r="I13" s="59"/>
+      <c r="J13" s="60"/>
+      <c r="K13" s="59"/>
+      <c r="L13" s="54"/>
+      <c r="M13" s="54"/>
+      <c r="N13" s="54"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="54"/>
+      <c r="Q13" s="54"/>
+      <c r="R13" s="54"/>
+      <c r="S13" s="61"/>
+      <c r="T13" s="62"/>
+      <c r="U13" s="63"/>
+      <c r="V13" s="39"/>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="45" t="n">
+      <c r="A14" s="46" t="n">
         <v>1011</v>
       </c>
-      <c r="B14" s="46" t="s">
+      <c r="B14" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="47" t="s">
+      <c r="C14" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="48" t="n">
+      <c r="D14" s="49" t="n">
         <v>0.375</v>
       </c>
-      <c r="E14" s="48" t="n">
+      <c r="E14" s="49" t="n">
         <v>0.0486111111111111</v>
       </c>
-      <c r="F14" s="48"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="58"/>
-      <c r="J14" s="59"/>
-      <c r="K14" s="58"/>
-      <c r="L14" s="53"/>
-      <c r="M14" s="53"/>
-      <c r="N14" s="53"/>
-      <c r="O14" s="53"/>
-      <c r="P14" s="53"/>
-      <c r="Q14" s="53"/>
-      <c r="R14" s="53"/>
-      <c r="S14" s="60"/>
-      <c r="T14" s="61"/>
-      <c r="U14" s="62"/>
-      <c r="V14" s="38"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="50"/>
+      <c r="H14" s="50"/>
+      <c r="I14" s="59"/>
+      <c r="J14" s="60"/>
+      <c r="K14" s="59"/>
+      <c r="L14" s="54"/>
+      <c r="M14" s="54"/>
+      <c r="N14" s="54"/>
+      <c r="O14" s="54"/>
+      <c r="P14" s="54"/>
+      <c r="Q14" s="54"/>
+      <c r="R14" s="54"/>
+      <c r="S14" s="61"/>
+      <c r="T14" s="62"/>
+      <c r="U14" s="63"/>
+      <c r="V14" s="39"/>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="45" t="n">
+      <c r="A15" s="46" t="n">
         <v>1012</v>
       </c>
-      <c r="B15" s="46" t="s">
+      <c r="B15" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C15" s="47" t="s">
+      <c r="C15" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="48" t="n">
+      <c r="D15" s="49" t="n">
         <v>0.385416666666667</v>
       </c>
-      <c r="E15" s="48" t="n">
+      <c r="E15" s="49" t="n">
         <v>0.0555555555555556</v>
       </c>
-      <c r="F15" s="48"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="49"/>
-      <c r="I15" s="58"/>
-      <c r="J15" s="59"/>
-      <c r="K15" s="58"/>
-      <c r="L15" s="53"/>
-      <c r="M15" s="53"/>
-      <c r="N15" s="53"/>
-      <c r="O15" s="53"/>
-      <c r="P15" s="53"/>
-      <c r="Q15" s="53"/>
-      <c r="R15" s="53"/>
-      <c r="S15" s="60"/>
-      <c r="T15" s="61"/>
-      <c r="U15" s="62"/>
-      <c r="V15" s="38"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="50"/>
+      <c r="H15" s="50"/>
+      <c r="I15" s="59"/>
+      <c r="J15" s="60"/>
+      <c r="K15" s="59"/>
+      <c r="L15" s="54"/>
+      <c r="M15" s="54"/>
+      <c r="N15" s="54"/>
+      <c r="O15" s="54"/>
+      <c r="P15" s="54"/>
+      <c r="Q15" s="54"/>
+      <c r="R15" s="54"/>
+      <c r="S15" s="61"/>
+      <c r="T15" s="62"/>
+      <c r="U15" s="63"/>
+      <c r="V15" s="39"/>
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="45" t="n">
+      <c r="A16" s="46" t="n">
         <v>1013</v>
       </c>
-      <c r="B16" s="46" t="s">
+      <c r="B16" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="47" t="s">
+      <c r="C16" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="48" t="n">
+      <c r="D16" s="49" t="n">
         <v>0.395833333333333</v>
       </c>
-      <c r="E16" s="48" t="n">
+      <c r="E16" s="49" t="n">
         <v>0.0590277777777778</v>
       </c>
-      <c r="F16" s="48"/>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49"/>
-      <c r="I16" s="58"/>
-      <c r="J16" s="59"/>
-      <c r="K16" s="58"/>
-      <c r="L16" s="53"/>
-      <c r="M16" s="53"/>
-      <c r="N16" s="53"/>
-      <c r="O16" s="53"/>
-      <c r="P16" s="53"/>
-      <c r="Q16" s="53"/>
-      <c r="R16" s="53"/>
-      <c r="S16" s="60"/>
-      <c r="T16" s="61"/>
-      <c r="U16" s="62"/>
-      <c r="V16" s="38"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="50"/>
+      <c r="H16" s="50"/>
+      <c r="I16" s="59"/>
+      <c r="J16" s="60"/>
+      <c r="K16" s="59"/>
+      <c r="L16" s="54"/>
+      <c r="M16" s="54"/>
+      <c r="N16" s="54"/>
+      <c r="O16" s="54"/>
+      <c r="P16" s="54"/>
+      <c r="Q16" s="54"/>
+      <c r="R16" s="54"/>
+      <c r="S16" s="61"/>
+      <c r="T16" s="62"/>
+      <c r="U16" s="63"/>
+      <c r="V16" s="39"/>
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="45" t="n">
+      <c r="A17" s="46" t="n">
         <v>1014</v>
       </c>
-      <c r="B17" s="46" t="s">
+      <c r="B17" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="47" t="s">
+      <c r="C17" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="48" t="n">
+      <c r="D17" s="49" t="n">
         <v>0.40625</v>
       </c>
-      <c r="E17" s="48" t="n">
+      <c r="E17" s="49" t="n">
         <v>0.0381944444444445</v>
       </c>
-      <c r="F17" s="48"/>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49"/>
-      <c r="I17" s="58"/>
-      <c r="J17" s="59"/>
-      <c r="K17" s="58"/>
-      <c r="L17" s="53"/>
-      <c r="M17" s="53"/>
-      <c r="N17" s="53"/>
-      <c r="O17" s="53"/>
-      <c r="P17" s="53"/>
-      <c r="Q17" s="53"/>
-      <c r="R17" s="53"/>
-      <c r="S17" s="60"/>
-      <c r="T17" s="61"/>
-      <c r="U17" s="62"/>
-      <c r="V17" s="38"/>
+      <c r="F17" s="49"/>
+      <c r="G17" s="50"/>
+      <c r="H17" s="50"/>
+      <c r="I17" s="59"/>
+      <c r="J17" s="60"/>
+      <c r="K17" s="59"/>
+      <c r="L17" s="54"/>
+      <c r="M17" s="54"/>
+      <c r="N17" s="54"/>
+      <c r="O17" s="54"/>
+      <c r="P17" s="54"/>
+      <c r="Q17" s="54"/>
+      <c r="R17" s="54"/>
+      <c r="S17" s="61"/>
+      <c r="T17" s="62"/>
+      <c r="U17" s="63"/>
+      <c r="V17" s="39"/>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="45" t="n">
+      <c r="A18" s="46" t="n">
         <v>1015</v>
       </c>
-      <c r="B18" s="46" t="s">
+      <c r="B18" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C18" s="47" t="s">
+      <c r="C18" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="48" t="n">
+      <c r="D18" s="49" t="n">
         <v>0.416666666666667</v>
       </c>
-      <c r="E18" s="48" t="n">
+      <c r="E18" s="49" t="n">
         <v>0.0381944444444445</v>
       </c>
-      <c r="F18" s="48"/>
-      <c r="G18" s="49"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="58"/>
-      <c r="J18" s="59"/>
-      <c r="K18" s="58"/>
-      <c r="L18" s="53"/>
-      <c r="M18" s="53"/>
-      <c r="N18" s="53"/>
-      <c r="O18" s="53"/>
-      <c r="P18" s="53"/>
-      <c r="Q18" s="53"/>
-      <c r="R18" s="53"/>
-      <c r="S18" s="60"/>
-      <c r="T18" s="61"/>
-      <c r="U18" s="62"/>
-      <c r="V18" s="38"/>
+      <c r="F18" s="49"/>
+      <c r="G18" s="50"/>
+      <c r="H18" s="50"/>
+      <c r="I18" s="59"/>
+      <c r="J18" s="60"/>
+      <c r="K18" s="59"/>
+      <c r="L18" s="54"/>
+      <c r="M18" s="54"/>
+      <c r="N18" s="54"/>
+      <c r="O18" s="54"/>
+      <c r="P18" s="54"/>
+      <c r="Q18" s="54"/>
+      <c r="R18" s="54"/>
+      <c r="S18" s="61"/>
+      <c r="T18" s="62"/>
+      <c r="U18" s="63"/>
+      <c r="V18" s="39"/>
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="45" t="n">
+      <c r="A19" s="46" t="n">
         <v>1016</v>
       </c>
-      <c r="B19" s="46" t="s">
+      <c r="B19" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C19" s="47" t="s">
+      <c r="C19" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="48" t="n">
+      <c r="D19" s="49" t="n">
         <v>0.427083333333333</v>
       </c>
-      <c r="E19" s="48" t="n">
+      <c r="E19" s="49" t="n">
         <v>0.0416666666666667</v>
       </c>
-      <c r="F19" s="48"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="49"/>
-      <c r="I19" s="58"/>
-      <c r="J19" s="59"/>
-      <c r="K19" s="58"/>
-      <c r="L19" s="53"/>
-      <c r="M19" s="53"/>
-      <c r="N19" s="53"/>
-      <c r="O19" s="53"/>
-      <c r="P19" s="53"/>
-      <c r="Q19" s="53"/>
-      <c r="R19" s="53"/>
-      <c r="S19" s="60"/>
-      <c r="T19" s="61"/>
-      <c r="U19" s="62"/>
-      <c r="V19" s="38"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="50"/>
+      <c r="I19" s="59"/>
+      <c r="J19" s="60"/>
+      <c r="K19" s="59"/>
+      <c r="L19" s="54"/>
+      <c r="M19" s="54"/>
+      <c r="N19" s="54"/>
+      <c r="O19" s="54"/>
+      <c r="P19" s="54"/>
+      <c r="Q19" s="54"/>
+      <c r="R19" s="54"/>
+      <c r="S19" s="61"/>
+      <c r="T19" s="62"/>
+      <c r="U19" s="63"/>
+      <c r="V19" s="39"/>
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="45" t="n">
+      <c r="A20" s="46" t="n">
         <v>1017</v>
       </c>
-      <c r="B20" s="46" t="s">
+      <c r="B20" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C20" s="47" t="s">
+      <c r="C20" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="48" t="n">
+      <c r="D20" s="49" t="n">
         <v>0.4375</v>
       </c>
-      <c r="E20" s="48" t="n">
+      <c r="E20" s="49" t="n">
         <v>0.0416666666666667</v>
       </c>
-      <c r="F20" s="48"/>
-      <c r="G20" s="49"/>
-      <c r="H20" s="49"/>
-      <c r="I20" s="58"/>
-      <c r="J20" s="59"/>
-      <c r="K20" s="58"/>
-      <c r="L20" s="53"/>
-      <c r="M20" s="53"/>
-      <c r="N20" s="53"/>
-      <c r="O20" s="53"/>
-      <c r="P20" s="53"/>
-      <c r="Q20" s="53"/>
-      <c r="R20" s="53"/>
-      <c r="S20" s="60"/>
-      <c r="T20" s="61"/>
-      <c r="U20" s="62"/>
-      <c r="V20" s="38"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="50"/>
+      <c r="H20" s="50"/>
+      <c r="I20" s="59"/>
+      <c r="J20" s="60"/>
+      <c r="K20" s="59"/>
+      <c r="L20" s="54"/>
+      <c r="M20" s="54"/>
+      <c r="N20" s="54"/>
+      <c r="O20" s="54"/>
+      <c r="P20" s="54"/>
+      <c r="Q20" s="54"/>
+      <c r="R20" s="54"/>
+      <c r="S20" s="61"/>
+      <c r="T20" s="62"/>
+      <c r="U20" s="63"/>
+      <c r="V20" s="39"/>
     </row>
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="45" t="n">
+      <c r="A21" s="46" t="n">
         <v>1018</v>
       </c>
-      <c r="B21" s="46" t="s">
+      <c r="B21" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C21" s="47" t="s">
+      <c r="C21" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="48" t="n">
+      <c r="D21" s="49" t="n">
         <v>0.447916666666667</v>
       </c>
-      <c r="E21" s="48" t="n">
+      <c r="E21" s="49" t="n">
         <v>0.0590277777777778</v>
       </c>
-      <c r="F21" s="48"/>
-      <c r="G21" s="49"/>
-      <c r="H21" s="49"/>
-      <c r="I21" s="58"/>
-      <c r="J21" s="59"/>
-      <c r="K21" s="58"/>
-      <c r="L21" s="53"/>
-      <c r="M21" s="53"/>
-      <c r="N21" s="53"/>
-      <c r="O21" s="53"/>
-      <c r="P21" s="53"/>
-      <c r="Q21" s="53"/>
-      <c r="R21" s="53"/>
-      <c r="S21" s="60"/>
-      <c r="T21" s="61"/>
-      <c r="U21" s="62"/>
-      <c r="V21" s="38"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="50"/>
+      <c r="H21" s="50"/>
+      <c r="I21" s="59"/>
+      <c r="J21" s="60"/>
+      <c r="K21" s="59"/>
+      <c r="L21" s="54"/>
+      <c r="M21" s="54"/>
+      <c r="N21" s="54"/>
+      <c r="O21" s="54"/>
+      <c r="P21" s="54"/>
+      <c r="Q21" s="54"/>
+      <c r="R21" s="54"/>
+      <c r="S21" s="61"/>
+      <c r="T21" s="62"/>
+      <c r="U21" s="63"/>
+      <c r="V21" s="39"/>
     </row>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="45" t="n">
+      <c r="A22" s="46" t="n">
         <v>1019</v>
       </c>
-      <c r="B22" s="46" t="s">
+      <c r="B22" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="47" t="s">
+      <c r="C22" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="D22" s="48" t="n">
+      <c r="D22" s="49" t="n">
         <v>0.458333333333333</v>
       </c>
-      <c r="E22" s="48" t="n">
+      <c r="E22" s="49" t="n">
         <v>0.0659722222222222</v>
       </c>
-      <c r="F22" s="48"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="49"/>
-      <c r="I22" s="58"/>
-      <c r="J22" s="59"/>
-      <c r="K22" s="58"/>
-      <c r="L22" s="53"/>
-      <c r="M22" s="53"/>
-      <c r="N22" s="53"/>
-      <c r="O22" s="53"/>
-      <c r="P22" s="53"/>
-      <c r="Q22" s="53"/>
-      <c r="R22" s="53"/>
-      <c r="S22" s="60"/>
-      <c r="T22" s="61"/>
-      <c r="U22" s="62"/>
-      <c r="V22" s="38"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="50"/>
+      <c r="I22" s="59"/>
+      <c r="J22" s="60"/>
+      <c r="K22" s="59"/>
+      <c r="L22" s="54"/>
+      <c r="M22" s="54"/>
+      <c r="N22" s="54"/>
+      <c r="O22" s="54"/>
+      <c r="P22" s="54"/>
+      <c r="Q22" s="54"/>
+      <c r="R22" s="54"/>
+      <c r="S22" s="61"/>
+      <c r="T22" s="62"/>
+      <c r="U22" s="63"/>
+      <c r="V22" s="39"/>
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="45" t="n">
+      <c r="A23" s="46" t="n">
         <v>1020</v>
       </c>
-      <c r="B23" s="46" t="s">
+      <c r="B23" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="47" t="s">
+      <c r="C23" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="D23" s="48" t="n">
+      <c r="D23" s="49" t="n">
         <v>0.46875</v>
       </c>
-      <c r="E23" s="48" t="n">
+      <c r="E23" s="49" t="n">
         <v>0.0659722222222222</v>
       </c>
-      <c r="F23" s="48"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="49"/>
-      <c r="I23" s="58"/>
-      <c r="J23" s="59"/>
-      <c r="K23" s="58"/>
-      <c r="L23" s="53"/>
-      <c r="M23" s="53"/>
-      <c r="N23" s="53"/>
-      <c r="O23" s="53"/>
-      <c r="P23" s="53"/>
-      <c r="Q23" s="53"/>
-      <c r="R23" s="53"/>
-      <c r="S23" s="60"/>
-      <c r="T23" s="61"/>
-      <c r="U23" s="62"/>
-      <c r="V23" s="38"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="50"/>
+      <c r="H23" s="50"/>
+      <c r="I23" s="59"/>
+      <c r="J23" s="60"/>
+      <c r="K23" s="59"/>
+      <c r="L23" s="54"/>
+      <c r="M23" s="54"/>
+      <c r="N23" s="54"/>
+      <c r="O23" s="54"/>
+      <c r="P23" s="54"/>
+      <c r="Q23" s="54"/>
+      <c r="R23" s="54"/>
+      <c r="S23" s="61"/>
+      <c r="T23" s="62"/>
+      <c r="U23" s="63"/>
+      <c r="V23" s="39"/>
     </row>
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="45" t="n">
+      <c r="A24" s="46" t="n">
         <v>1021</v>
       </c>
-      <c r="B24" s="46" t="s">
+      <c r="B24" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="47" t="s">
+      <c r="C24" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="D24" s="48" t="n">
+      <c r="D24" s="49" t="n">
         <v>0.479166666666667</v>
       </c>
-      <c r="E24" s="48" t="n">
+      <c r="E24" s="49" t="n">
         <v>0.0659722222222222</v>
       </c>
-      <c r="F24" s="48"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="49"/>
-      <c r="I24" s="58"/>
-      <c r="J24" s="59"/>
-      <c r="K24" s="58"/>
-      <c r="L24" s="53"/>
-      <c r="M24" s="53"/>
-      <c r="N24" s="53"/>
-      <c r="O24" s="53"/>
-      <c r="P24" s="53"/>
-      <c r="Q24" s="53"/>
-      <c r="R24" s="53"/>
-      <c r="S24" s="60"/>
-      <c r="T24" s="61"/>
-      <c r="U24" s="62"/>
-      <c r="V24" s="38"/>
+      <c r="F24" s="49"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="59"/>
+      <c r="J24" s="60"/>
+      <c r="K24" s="59"/>
+      <c r="L24" s="54"/>
+      <c r="M24" s="54"/>
+      <c r="N24" s="54"/>
+      <c r="O24" s="54"/>
+      <c r="P24" s="54"/>
+      <c r="Q24" s="54"/>
+      <c r="R24" s="54"/>
+      <c r="S24" s="61"/>
+      <c r="T24" s="62"/>
+      <c r="U24" s="63"/>
+      <c r="V24" s="39"/>
     </row>
     <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="45" t="n">
+      <c r="A25" s="46" t="n">
         <v>1022</v>
       </c>
-      <c r="B25" s="46" t="s">
+      <c r="B25" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C25" s="47" t="s">
+      <c r="C25" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="D25" s="48" t="n">
+      <c r="D25" s="49" t="n">
         <v>0.489583333333333</v>
       </c>
-      <c r="E25" s="48" t="n">
+      <c r="E25" s="49" t="n">
         <v>0.0625</v>
       </c>
-      <c r="F25" s="48"/>
-      <c r="G25" s="49"/>
-      <c r="H25" s="49"/>
-      <c r="I25" s="58"/>
-      <c r="J25" s="59"/>
-      <c r="K25" s="58"/>
-      <c r="L25" s="53"/>
-      <c r="M25" s="53"/>
-      <c r="N25" s="53"/>
-      <c r="O25" s="53"/>
-      <c r="P25" s="53"/>
-      <c r="Q25" s="53"/>
-      <c r="R25" s="53"/>
-      <c r="S25" s="60"/>
-      <c r="T25" s="61"/>
-      <c r="U25" s="62"/>
-      <c r="V25" s="38"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="50"/>
+      <c r="H25" s="50"/>
+      <c r="I25" s="59"/>
+      <c r="J25" s="60"/>
+      <c r="K25" s="59"/>
+      <c r="L25" s="54"/>
+      <c r="M25" s="54"/>
+      <c r="N25" s="54"/>
+      <c r="O25" s="54"/>
+      <c r="P25" s="54"/>
+      <c r="Q25" s="54"/>
+      <c r="R25" s="54"/>
+      <c r="S25" s="61"/>
+      <c r="T25" s="62"/>
+      <c r="U25" s="63"/>
+      <c r="V25" s="39"/>
     </row>
     <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="45" t="n">
+      <c r="A26" s="46" t="n">
         <v>1023</v>
       </c>
-      <c r="B26" s="46" t="s">
+      <c r="B26" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="47" t="s">
+      <c r="C26" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="D26" s="48" t="n">
+      <c r="D26" s="49" t="n">
         <v>0.5</v>
       </c>
-      <c r="E26" s="48" t="n">
+      <c r="E26" s="49" t="n">
         <v>0.0625</v>
       </c>
-      <c r="F26" s="48"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="58"/>
-      <c r="J26" s="59"/>
-      <c r="K26" s="58"/>
-      <c r="L26" s="53"/>
-      <c r="M26" s="53"/>
-      <c r="N26" s="53"/>
-      <c r="O26" s="53"/>
-      <c r="P26" s="53"/>
-      <c r="Q26" s="53"/>
-      <c r="R26" s="53"/>
-      <c r="S26" s="60"/>
-      <c r="T26" s="61"/>
-      <c r="U26" s="62"/>
-      <c r="V26" s="38"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="50"/>
+      <c r="H26" s="50"/>
+      <c r="I26" s="59"/>
+      <c r="J26" s="60"/>
+      <c r="K26" s="59"/>
+      <c r="L26" s="54"/>
+      <c r="M26" s="54"/>
+      <c r="N26" s="54"/>
+      <c r="O26" s="54"/>
+      <c r="P26" s="54"/>
+      <c r="Q26" s="54"/>
+      <c r="R26" s="54"/>
+      <c r="S26" s="61"/>
+      <c r="T26" s="62"/>
+      <c r="U26" s="63"/>
+      <c r="V26" s="39"/>
     </row>
     <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="45" t="n">
+      <c r="A27" s="46" t="n">
         <v>1024</v>
       </c>
-      <c r="B27" s="46" t="s">
+      <c r="B27" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C27" s="47" t="s">
+      <c r="C27" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="D27" s="48" t="n">
+      <c r="D27" s="49" t="n">
         <v>0.510416666666667</v>
       </c>
-      <c r="E27" s="48" t="n">
+      <c r="E27" s="49" t="n">
         <v>0.0416666666666667</v>
       </c>
-      <c r="F27" s="48"/>
-      <c r="G27" s="49"/>
-      <c r="H27" s="49"/>
-      <c r="I27" s="58"/>
-      <c r="J27" s="59"/>
-      <c r="K27" s="58"/>
-      <c r="L27" s="53"/>
-      <c r="M27" s="53"/>
-      <c r="N27" s="53"/>
-      <c r="O27" s="53"/>
-      <c r="P27" s="53"/>
-      <c r="Q27" s="53"/>
-      <c r="R27" s="53"/>
-      <c r="S27" s="60"/>
-      <c r="T27" s="61"/>
-      <c r="U27" s="62"/>
-      <c r="V27" s="38"/>
+      <c r="F27" s="49"/>
+      <c r="G27" s="50"/>
+      <c r="H27" s="50"/>
+      <c r="I27" s="59"/>
+      <c r="J27" s="60"/>
+      <c r="K27" s="59"/>
+      <c r="L27" s="54"/>
+      <c r="M27" s="54"/>
+      <c r="N27" s="54"/>
+      <c r="O27" s="54"/>
+      <c r="P27" s="54"/>
+      <c r="Q27" s="54"/>
+      <c r="R27" s="54"/>
+      <c r="S27" s="61"/>
+      <c r="T27" s="62"/>
+      <c r="U27" s="63"/>
+      <c r="V27" s="39"/>
     </row>
     <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="45"/>
-      <c r="B28" s="46"/>
-      <c r="C28" s="47"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="48"/>
-      <c r="F28" s="48"/>
-      <c r="G28" s="49"/>
-      <c r="H28" s="49"/>
-      <c r="I28" s="58"/>
-      <c r="J28" s="59"/>
-      <c r="K28" s="58"/>
-      <c r="L28" s="53"/>
-      <c r="M28" s="53"/>
-      <c r="N28" s="53"/>
-      <c r="O28" s="53"/>
-      <c r="P28" s="53"/>
-      <c r="Q28" s="53"/>
-      <c r="R28" s="53"/>
-      <c r="S28" s="60"/>
-      <c r="T28" s="61"/>
-      <c r="U28" s="62"/>
-      <c r="V28" s="38"/>
+      <c r="A28" s="46"/>
+      <c r="B28" s="47"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="48"/>
+      <c r="E28" s="49"/>
+      <c r="F28" s="49"/>
+      <c r="G28" s="50"/>
+      <c r="H28" s="50"/>
+      <c r="I28" s="59"/>
+      <c r="J28" s="60"/>
+      <c r="K28" s="59"/>
+      <c r="L28" s="54"/>
+      <c r="M28" s="54"/>
+      <c r="N28" s="54"/>
+      <c r="O28" s="54"/>
+      <c r="P28" s="54"/>
+      <c r="Q28" s="54"/>
+      <c r="R28" s="54"/>
+      <c r="S28" s="61"/>
+      <c r="T28" s="62"/>
+      <c r="U28" s="63"/>
+      <c r="V28" s="39"/>
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="45"/>
-      <c r="B29" s="46"/>
-      <c r="C29" s="47"/>
-      <c r="D29" s="47"/>
-      <c r="E29" s="48"/>
-      <c r="F29" s="48"/>
-      <c r="G29" s="49"/>
-      <c r="H29" s="49"/>
-      <c r="I29" s="58"/>
-      <c r="J29" s="59"/>
-      <c r="K29" s="58"/>
-      <c r="L29" s="53"/>
-      <c r="M29" s="53"/>
-      <c r="N29" s="53"/>
-      <c r="O29" s="53"/>
-      <c r="P29" s="53"/>
-      <c r="Q29" s="53"/>
-      <c r="R29" s="53"/>
-      <c r="S29" s="60"/>
-      <c r="T29" s="61"/>
-      <c r="U29" s="62"/>
-      <c r="V29" s="38"/>
+      <c r="A29" s="46"/>
+      <c r="B29" s="47"/>
+      <c r="C29" s="48"/>
+      <c r="D29" s="48"/>
+      <c r="E29" s="49"/>
+      <c r="F29" s="49"/>
+      <c r="G29" s="50"/>
+      <c r="H29" s="50"/>
+      <c r="I29" s="59"/>
+      <c r="J29" s="60"/>
+      <c r="K29" s="59"/>
+      <c r="L29" s="54"/>
+      <c r="M29" s="54"/>
+      <c r="N29" s="54"/>
+      <c r="O29" s="54"/>
+      <c r="P29" s="54"/>
+      <c r="Q29" s="54"/>
+      <c r="R29" s="54"/>
+      <c r="S29" s="61"/>
+      <c r="T29" s="62"/>
+      <c r="U29" s="63"/>
+      <c r="V29" s="39"/>
     </row>
     <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="45"/>
-      <c r="B30" s="46"/>
-      <c r="C30" s="47"/>
-      <c r="D30" s="47"/>
-      <c r="E30" s="48"/>
-      <c r="F30" s="48"/>
-      <c r="G30" s="49"/>
-      <c r="H30" s="49"/>
-      <c r="I30" s="58"/>
-      <c r="J30" s="59"/>
-      <c r="K30" s="58"/>
-      <c r="L30" s="53"/>
-      <c r="M30" s="53"/>
-      <c r="N30" s="53"/>
-      <c r="O30" s="53"/>
-      <c r="P30" s="53"/>
-      <c r="Q30" s="53"/>
-      <c r="R30" s="53"/>
-      <c r="S30" s="60"/>
-      <c r="T30" s="61"/>
-      <c r="U30" s="62"/>
-      <c r="V30" s="38"/>
+      <c r="A30" s="46"/>
+      <c r="B30" s="47"/>
+      <c r="C30" s="48"/>
+      <c r="D30" s="48"/>
+      <c r="E30" s="49"/>
+      <c r="F30" s="49"/>
+      <c r="G30" s="50"/>
+      <c r="H30" s="50"/>
+      <c r="I30" s="59"/>
+      <c r="J30" s="60"/>
+      <c r="K30" s="59"/>
+      <c r="L30" s="54"/>
+      <c r="M30" s="54"/>
+      <c r="N30" s="54"/>
+      <c r="O30" s="54"/>
+      <c r="P30" s="54"/>
+      <c r="Q30" s="54"/>
+      <c r="R30" s="54"/>
+      <c r="S30" s="61"/>
+      <c r="T30" s="62"/>
+      <c r="U30" s="63"/>
+      <c r="V30" s="39"/>
     </row>
     <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="45"/>
-      <c r="B31" s="46"/>
-      <c r="C31" s="47"/>
-      <c r="D31" s="47"/>
-      <c r="E31" s="48"/>
-      <c r="F31" s="48"/>
-      <c r="G31" s="49"/>
-      <c r="H31" s="49"/>
-      <c r="I31" s="58"/>
-      <c r="J31" s="59"/>
-      <c r="K31" s="58"/>
-      <c r="L31" s="53"/>
-      <c r="M31" s="53"/>
-      <c r="N31" s="53"/>
-      <c r="O31" s="53"/>
-      <c r="P31" s="53"/>
-      <c r="Q31" s="53"/>
-      <c r="R31" s="53"/>
-      <c r="S31" s="60"/>
-      <c r="T31" s="61"/>
-      <c r="U31" s="62"/>
-      <c r="V31" s="38"/>
+      <c r="A31" s="46"/>
+      <c r="B31" s="47"/>
+      <c r="C31" s="48"/>
+      <c r="D31" s="48"/>
+      <c r="E31" s="49"/>
+      <c r="F31" s="49"/>
+      <c r="G31" s="50"/>
+      <c r="H31" s="50"/>
+      <c r="I31" s="59"/>
+      <c r="J31" s="60"/>
+      <c r="K31" s="59"/>
+      <c r="L31" s="54"/>
+      <c r="M31" s="54"/>
+      <c r="N31" s="54"/>
+      <c r="O31" s="54"/>
+      <c r="P31" s="54"/>
+      <c r="Q31" s="54"/>
+      <c r="R31" s="54"/>
+      <c r="S31" s="61"/>
+      <c r="T31" s="62"/>
+      <c r="U31" s="63"/>
+      <c r="V31" s="39"/>
     </row>
     <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="45"/>
-      <c r="B32" s="46"/>
-      <c r="C32" s="47"/>
-      <c r="D32" s="47"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="48"/>
-      <c r="G32" s="49"/>
-      <c r="H32" s="49"/>
-      <c r="I32" s="58"/>
-      <c r="J32" s="59"/>
-      <c r="K32" s="58"/>
-      <c r="L32" s="53"/>
-      <c r="M32" s="53"/>
-      <c r="N32" s="53"/>
-      <c r="O32" s="53"/>
-      <c r="P32" s="53"/>
-      <c r="Q32" s="53"/>
-      <c r="R32" s="53"/>
-      <c r="S32" s="60"/>
-      <c r="T32" s="61"/>
-      <c r="U32" s="62"/>
-      <c r="V32" s="38"/>
+      <c r="A32" s="46"/>
+      <c r="B32" s="47"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="48"/>
+      <c r="E32" s="49"/>
+      <c r="F32" s="49"/>
+      <c r="G32" s="50"/>
+      <c r="H32" s="50"/>
+      <c r="I32" s="59"/>
+      <c r="J32" s="60"/>
+      <c r="K32" s="59"/>
+      <c r="L32" s="54"/>
+      <c r="M32" s="54"/>
+      <c r="N32" s="54"/>
+      <c r="O32" s="54"/>
+      <c r="P32" s="54"/>
+      <c r="Q32" s="54"/>
+      <c r="R32" s="54"/>
+      <c r="S32" s="61"/>
+      <c r="T32" s="62"/>
+      <c r="U32" s="63"/>
+      <c r="V32" s="39"/>
     </row>
     <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="45"/>
-      <c r="B33" s="46"/>
-      <c r="C33" s="47"/>
-      <c r="D33" s="47"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="49"/>
-      <c r="H33" s="49"/>
-      <c r="I33" s="58"/>
-      <c r="J33" s="59"/>
-      <c r="K33" s="58"/>
-      <c r="L33" s="53"/>
-      <c r="M33" s="53"/>
-      <c r="N33" s="53"/>
-      <c r="O33" s="53"/>
-      <c r="P33" s="53"/>
-      <c r="Q33" s="53"/>
-      <c r="R33" s="53"/>
-      <c r="S33" s="60"/>
-      <c r="T33" s="61"/>
-      <c r="U33" s="62"/>
-      <c r="V33" s="38"/>
+      <c r="A33" s="46"/>
+      <c r="B33" s="47"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="48"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="49"/>
+      <c r="G33" s="50"/>
+      <c r="H33" s="50"/>
+      <c r="I33" s="59"/>
+      <c r="J33" s="60"/>
+      <c r="K33" s="59"/>
+      <c r="L33" s="54"/>
+      <c r="M33" s="54"/>
+      <c r="N33" s="54"/>
+      <c r="O33" s="54"/>
+      <c r="P33" s="54"/>
+      <c r="Q33" s="54"/>
+      <c r="R33" s="54"/>
+      <c r="S33" s="61"/>
+      <c r="T33" s="62"/>
+      <c r="U33" s="63"/>
+      <c r="V33" s="39"/>
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="45"/>
-      <c r="B34" s="46"/>
-      <c r="C34" s="47"/>
-      <c r="D34" s="47"/>
-      <c r="E34" s="48"/>
-      <c r="F34" s="48"/>
-      <c r="G34" s="49"/>
-      <c r="H34" s="49"/>
-      <c r="I34" s="58"/>
-      <c r="J34" s="59"/>
-      <c r="K34" s="58"/>
-      <c r="L34" s="53"/>
-      <c r="M34" s="53"/>
-      <c r="N34" s="53"/>
-      <c r="O34" s="53"/>
-      <c r="P34" s="53"/>
-      <c r="Q34" s="53"/>
-      <c r="R34" s="53"/>
-      <c r="S34" s="60"/>
-      <c r="T34" s="61"/>
-      <c r="U34" s="62"/>
-      <c r="V34" s="38"/>
+      <c r="A34" s="46"/>
+      <c r="B34" s="47"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="48"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="49"/>
+      <c r="G34" s="50"/>
+      <c r="H34" s="50"/>
+      <c r="I34" s="59"/>
+      <c r="J34" s="60"/>
+      <c r="K34" s="59"/>
+      <c r="L34" s="54"/>
+      <c r="M34" s="54"/>
+      <c r="N34" s="54"/>
+      <c r="O34" s="54"/>
+      <c r="P34" s="54"/>
+      <c r="Q34" s="54"/>
+      <c r="R34" s="54"/>
+      <c r="S34" s="61"/>
+      <c r="T34" s="62"/>
+      <c r="U34" s="63"/>
+      <c r="V34" s="39"/>
     </row>
     <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="45"/>
-      <c r="B35" s="46"/>
-      <c r="C35" s="47"/>
-      <c r="D35" s="47"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="49"/>
-      <c r="H35" s="49"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="59"/>
-      <c r="K35" s="58"/>
-      <c r="L35" s="53"/>
-      <c r="M35" s="53"/>
-      <c r="N35" s="53"/>
-      <c r="O35" s="53"/>
-      <c r="P35" s="53"/>
-      <c r="Q35" s="53"/>
-      <c r="R35" s="53"/>
-      <c r="S35" s="60"/>
-      <c r="T35" s="61"/>
-      <c r="U35" s="62"/>
-      <c r="V35" s="38"/>
+      <c r="A35" s="46"/>
+      <c r="B35" s="47"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="48"/>
+      <c r="E35" s="49"/>
+      <c r="F35" s="49"/>
+      <c r="G35" s="50"/>
+      <c r="H35" s="50"/>
+      <c r="I35" s="59"/>
+      <c r="J35" s="60"/>
+      <c r="K35" s="59"/>
+      <c r="L35" s="54"/>
+      <c r="M35" s="54"/>
+      <c r="N35" s="54"/>
+      <c r="O35" s="54"/>
+      <c r="P35" s="54"/>
+      <c r="Q35" s="54"/>
+      <c r="R35" s="54"/>
+      <c r="S35" s="61"/>
+      <c r="T35" s="62"/>
+      <c r="U35" s="63"/>
+      <c r="V35" s="39"/>
     </row>
     <row r="36" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="45"/>
-      <c r="B36" s="46"/>
-      <c r="C36" s="47"/>
-      <c r="D36" s="47"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="49"/>
-      <c r="H36" s="49"/>
-      <c r="I36" s="58"/>
-      <c r="J36" s="59"/>
-      <c r="K36" s="58"/>
-      <c r="L36" s="53"/>
-      <c r="M36" s="53"/>
-      <c r="N36" s="53"/>
-      <c r="O36" s="53"/>
-      <c r="P36" s="53"/>
-      <c r="Q36" s="53"/>
-      <c r="R36" s="53"/>
-      <c r="S36" s="60"/>
-      <c r="T36" s="61"/>
-      <c r="U36" s="62"/>
-      <c r="V36" s="38"/>
+      <c r="A36" s="46"/>
+      <c r="B36" s="47"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="49"/>
+      <c r="F36" s="49"/>
+      <c r="G36" s="50"/>
+      <c r="H36" s="50"/>
+      <c r="I36" s="59"/>
+      <c r="J36" s="60"/>
+      <c r="K36" s="59"/>
+      <c r="L36" s="54"/>
+      <c r="M36" s="54"/>
+      <c r="N36" s="54"/>
+      <c r="O36" s="54"/>
+      <c r="P36" s="54"/>
+      <c r="Q36" s="54"/>
+      <c r="R36" s="54"/>
+      <c r="S36" s="61"/>
+      <c r="T36" s="62"/>
+      <c r="U36" s="63"/>
+      <c r="V36" s="39"/>
     </row>
     <row r="37" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="45"/>
-      <c r="B37" s="46"/>
-      <c r="C37" s="47"/>
-      <c r="D37" s="47"/>
-      <c r="E37" s="48"/>
-      <c r="F37" s="48"/>
-      <c r="G37" s="49"/>
-      <c r="H37" s="49"/>
-      <c r="I37" s="58"/>
-      <c r="J37" s="59"/>
-      <c r="K37" s="58"/>
-      <c r="L37" s="53"/>
-      <c r="M37" s="53"/>
-      <c r="N37" s="53"/>
-      <c r="O37" s="53"/>
-      <c r="P37" s="53"/>
-      <c r="Q37" s="53"/>
-      <c r="R37" s="53"/>
-      <c r="S37" s="60"/>
-      <c r="T37" s="61"/>
-      <c r="U37" s="62"/>
-      <c r="V37" s="38"/>
+      <c r="A37" s="46"/>
+      <c r="B37" s="47"/>
+      <c r="C37" s="48"/>
+      <c r="D37" s="48"/>
+      <c r="E37" s="49"/>
+      <c r="F37" s="49"/>
+      <c r="G37" s="50"/>
+      <c r="H37" s="50"/>
+      <c r="I37" s="59"/>
+      <c r="J37" s="60"/>
+      <c r="K37" s="59"/>
+      <c r="L37" s="54"/>
+      <c r="M37" s="54"/>
+      <c r="N37" s="54"/>
+      <c r="O37" s="54"/>
+      <c r="P37" s="54"/>
+      <c r="Q37" s="54"/>
+      <c r="R37" s="54"/>
+      <c r="S37" s="61"/>
+      <c r="T37" s="62"/>
+      <c r="U37" s="63"/>
+      <c r="V37" s="39"/>
     </row>
     <row r="38" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="45"/>
-      <c r="B38" s="46"/>
-      <c r="C38" s="47"/>
-      <c r="D38" s="47"/>
-      <c r="E38" s="48"/>
-      <c r="F38" s="48"/>
-      <c r="G38" s="49"/>
-      <c r="H38" s="49"/>
-      <c r="I38" s="58"/>
-      <c r="J38" s="59"/>
-      <c r="K38" s="58"/>
-      <c r="L38" s="53"/>
-      <c r="M38" s="53"/>
-      <c r="N38" s="53"/>
-      <c r="O38" s="53"/>
-      <c r="P38" s="53"/>
-      <c r="Q38" s="53"/>
-      <c r="R38" s="53"/>
-      <c r="S38" s="60"/>
-      <c r="T38" s="61"/>
-      <c r="U38" s="62"/>
-      <c r="V38" s="38"/>
+      <c r="A38" s="46"/>
+      <c r="B38" s="47"/>
+      <c r="C38" s="48"/>
+      <c r="D38" s="48"/>
+      <c r="E38" s="49"/>
+      <c r="F38" s="49"/>
+      <c r="G38" s="50"/>
+      <c r="H38" s="50"/>
+      <c r="I38" s="59"/>
+      <c r="J38" s="60"/>
+      <c r="K38" s="59"/>
+      <c r="L38" s="54"/>
+      <c r="M38" s="54"/>
+      <c r="N38" s="54"/>
+      <c r="O38" s="54"/>
+      <c r="P38" s="54"/>
+      <c r="Q38" s="54"/>
+      <c r="R38" s="54"/>
+      <c r="S38" s="61"/>
+      <c r="T38" s="62"/>
+      <c r="U38" s="63"/>
+      <c r="V38" s="39"/>
     </row>
     <row r="39" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="45"/>
-      <c r="B39" s="46"/>
-      <c r="C39" s="47"/>
-      <c r="D39" s="47"/>
-      <c r="E39" s="48"/>
-      <c r="F39" s="48"/>
-      <c r="G39" s="49"/>
-      <c r="H39" s="49"/>
-      <c r="I39" s="58"/>
-      <c r="J39" s="59"/>
-      <c r="K39" s="58"/>
-      <c r="L39" s="53"/>
-      <c r="M39" s="53"/>
-      <c r="N39" s="53"/>
-      <c r="O39" s="53"/>
-      <c r="P39" s="53"/>
-      <c r="Q39" s="53"/>
-      <c r="R39" s="53"/>
-      <c r="S39" s="60"/>
-      <c r="T39" s="61"/>
-      <c r="U39" s="62"/>
-      <c r="V39" s="38"/>
+      <c r="A39" s="46"/>
+      <c r="B39" s="47"/>
+      <c r="C39" s="48"/>
+      <c r="D39" s="48"/>
+      <c r="E39" s="49"/>
+      <c r="F39" s="49"/>
+      <c r="G39" s="50"/>
+      <c r="H39" s="50"/>
+      <c r="I39" s="59"/>
+      <c r="J39" s="60"/>
+      <c r="K39" s="59"/>
+      <c r="L39" s="54"/>
+      <c r="M39" s="54"/>
+      <c r="N39" s="54"/>
+      <c r="O39" s="54"/>
+      <c r="P39" s="54"/>
+      <c r="Q39" s="54"/>
+      <c r="R39" s="54"/>
+      <c r="S39" s="61"/>
+      <c r="T39" s="62"/>
+      <c r="U39" s="63"/>
+      <c r="V39" s="39"/>
     </row>
     <row r="40" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="45"/>
-      <c r="B40" s="46"/>
-      <c r="C40" s="47"/>
-      <c r="D40" s="47"/>
-      <c r="E40" s="48"/>
-      <c r="F40" s="48"/>
-      <c r="G40" s="49"/>
-      <c r="H40" s="49"/>
-      <c r="I40" s="58"/>
-      <c r="J40" s="59"/>
-      <c r="K40" s="58"/>
-      <c r="L40" s="53"/>
-      <c r="M40" s="53"/>
-      <c r="N40" s="53"/>
-      <c r="O40" s="53"/>
-      <c r="P40" s="53"/>
-      <c r="Q40" s="53"/>
-      <c r="R40" s="53"/>
-      <c r="S40" s="60"/>
-      <c r="T40" s="61"/>
-      <c r="U40" s="62"/>
-      <c r="V40" s="38"/>
+      <c r="A40" s="46"/>
+      <c r="B40" s="47"/>
+      <c r="C40" s="48"/>
+      <c r="D40" s="48"/>
+      <c r="E40" s="49"/>
+      <c r="F40" s="49"/>
+      <c r="G40" s="50"/>
+      <c r="H40" s="50"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="59"/>
+      <c r="L40" s="54"/>
+      <c r="M40" s="54"/>
+      <c r="N40" s="54"/>
+      <c r="O40" s="54"/>
+      <c r="P40" s="54"/>
+      <c r="Q40" s="54"/>
+      <c r="R40" s="54"/>
+      <c r="S40" s="61"/>
+      <c r="T40" s="62"/>
+      <c r="U40" s="63"/>
+      <c r="V40" s="39"/>
     </row>
     <row r="41" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="45"/>
-      <c r="B41" s="46"/>
-      <c r="C41" s="47"/>
-      <c r="D41" s="47"/>
-      <c r="E41" s="48"/>
-      <c r="F41" s="48"/>
-      <c r="G41" s="49"/>
-      <c r="H41" s="49"/>
-      <c r="I41" s="58"/>
-      <c r="J41" s="59"/>
-      <c r="K41" s="58"/>
-      <c r="L41" s="53"/>
-      <c r="M41" s="53"/>
-      <c r="N41" s="53"/>
-      <c r="O41" s="53"/>
-      <c r="P41" s="53"/>
-      <c r="Q41" s="53"/>
-      <c r="R41" s="53"/>
-      <c r="S41" s="60"/>
-      <c r="T41" s="61"/>
-      <c r="U41" s="62"/>
-      <c r="V41" s="38"/>
+      <c r="A41" s="46"/>
+      <c r="B41" s="47"/>
+      <c r="C41" s="48"/>
+      <c r="D41" s="48"/>
+      <c r="E41" s="49"/>
+      <c r="F41" s="49"/>
+      <c r="G41" s="50"/>
+      <c r="H41" s="50"/>
+      <c r="I41" s="59"/>
+      <c r="J41" s="60"/>
+      <c r="K41" s="59"/>
+      <c r="L41" s="54"/>
+      <c r="M41" s="54"/>
+      <c r="N41" s="54"/>
+      <c r="O41" s="54"/>
+      <c r="P41" s="54"/>
+      <c r="Q41" s="54"/>
+      <c r="R41" s="54"/>
+      <c r="S41" s="61"/>
+      <c r="T41" s="62"/>
+      <c r="U41" s="63"/>
+      <c r="V41" s="39"/>
     </row>
     <row r="42" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="45"/>
-      <c r="B42" s="46"/>
-      <c r="C42" s="47"/>
-      <c r="D42" s="47"/>
-      <c r="E42" s="48"/>
-      <c r="F42" s="48"/>
-      <c r="G42" s="49"/>
-      <c r="H42" s="49"/>
-      <c r="I42" s="58"/>
-      <c r="J42" s="59"/>
-      <c r="K42" s="58"/>
-      <c r="L42" s="53"/>
-      <c r="M42" s="53"/>
-      <c r="N42" s="53"/>
-      <c r="O42" s="53"/>
-      <c r="P42" s="53"/>
-      <c r="Q42" s="53"/>
-      <c r="R42" s="53"/>
-      <c r="S42" s="60"/>
-      <c r="T42" s="61"/>
-      <c r="U42" s="62"/>
-      <c r="V42" s="38"/>
+      <c r="A42" s="46"/>
+      <c r="B42" s="47"/>
+      <c r="C42" s="48"/>
+      <c r="D42" s="48"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="49"/>
+      <c r="G42" s="50"/>
+      <c r="H42" s="50"/>
+      <c r="I42" s="59"/>
+      <c r="J42" s="60"/>
+      <c r="K42" s="59"/>
+      <c r="L42" s="54"/>
+      <c r="M42" s="54"/>
+      <c r="N42" s="54"/>
+      <c r="O42" s="54"/>
+      <c r="P42" s="54"/>
+      <c r="Q42" s="54"/>
+      <c r="R42" s="54"/>
+      <c r="S42" s="61"/>
+      <c r="T42" s="62"/>
+      <c r="U42" s="63"/>
+      <c r="V42" s="39"/>
     </row>
     <row r="43" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="45"/>
-      <c r="B43" s="46"/>
-      <c r="C43" s="47"/>
-      <c r="D43" s="47"/>
-      <c r="E43" s="48"/>
-      <c r="F43" s="48"/>
-      <c r="G43" s="49"/>
-      <c r="H43" s="49"/>
-      <c r="I43" s="58"/>
-      <c r="J43" s="59"/>
-      <c r="K43" s="58"/>
-      <c r="L43" s="53"/>
-      <c r="M43" s="53"/>
-      <c r="N43" s="53"/>
-      <c r="O43" s="53"/>
-      <c r="P43" s="53"/>
-      <c r="Q43" s="53"/>
-      <c r="R43" s="53"/>
-      <c r="S43" s="60"/>
-      <c r="T43" s="61"/>
-      <c r="U43" s="62"/>
-      <c r="V43" s="38"/>
+      <c r="A43" s="46"/>
+      <c r="B43" s="47"/>
+      <c r="C43" s="48"/>
+      <c r="D43" s="48"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="49"/>
+      <c r="G43" s="50"/>
+      <c r="H43" s="50"/>
+      <c r="I43" s="59"/>
+      <c r="J43" s="60"/>
+      <c r="K43" s="59"/>
+      <c r="L43" s="54"/>
+      <c r="M43" s="54"/>
+      <c r="N43" s="54"/>
+      <c r="O43" s="54"/>
+      <c r="P43" s="54"/>
+      <c r="Q43" s="54"/>
+      <c r="R43" s="54"/>
+      <c r="S43" s="61"/>
+      <c r="T43" s="62"/>
+      <c r="U43" s="63"/>
+      <c r="V43" s="39"/>
     </row>
     <row r="44" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="45"/>
-      <c r="B44" s="46"/>
-      <c r="C44" s="47"/>
-      <c r="D44" s="47"/>
-      <c r="E44" s="48"/>
-      <c r="F44" s="48"/>
-      <c r="G44" s="49"/>
-      <c r="H44" s="49"/>
-      <c r="I44" s="58"/>
-      <c r="J44" s="59"/>
-      <c r="K44" s="58"/>
-      <c r="L44" s="53"/>
-      <c r="M44" s="53"/>
-      <c r="N44" s="53"/>
-      <c r="O44" s="53"/>
-      <c r="P44" s="53"/>
-      <c r="Q44" s="53"/>
-      <c r="R44" s="53"/>
-      <c r="S44" s="60"/>
-      <c r="T44" s="61"/>
-      <c r="U44" s="62"/>
-      <c r="V44" s="38"/>
+      <c r="A44" s="46"/>
+      <c r="B44" s="47"/>
+      <c r="C44" s="48"/>
+      <c r="D44" s="48"/>
+      <c r="E44" s="49"/>
+      <c r="F44" s="49"/>
+      <c r="G44" s="50"/>
+      <c r="H44" s="50"/>
+      <c r="I44" s="59"/>
+      <c r="J44" s="60"/>
+      <c r="K44" s="59"/>
+      <c r="L44" s="54"/>
+      <c r="M44" s="54"/>
+      <c r="N44" s="54"/>
+      <c r="O44" s="54"/>
+      <c r="P44" s="54"/>
+      <c r="Q44" s="54"/>
+      <c r="R44" s="54"/>
+      <c r="S44" s="61"/>
+      <c r="T44" s="62"/>
+      <c r="U44" s="63"/>
+      <c r="V44" s="39"/>
     </row>
     <row r="45" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="45"/>
-      <c r="B45" s="46"/>
-      <c r="C45" s="47"/>
-      <c r="D45" s="47"/>
-      <c r="E45" s="48"/>
-      <c r="F45" s="48"/>
-      <c r="G45" s="49"/>
-      <c r="H45" s="49"/>
-      <c r="I45" s="58"/>
-      <c r="J45" s="59"/>
-      <c r="K45" s="58"/>
-      <c r="L45" s="53"/>
-      <c r="M45" s="53"/>
-      <c r="N45" s="53"/>
-      <c r="O45" s="53"/>
-      <c r="P45" s="53"/>
-      <c r="Q45" s="53"/>
-      <c r="R45" s="53"/>
-      <c r="S45" s="60"/>
-      <c r="T45" s="61"/>
-      <c r="U45" s="62"/>
-      <c r="V45" s="38"/>
+      <c r="A45" s="46"/>
+      <c r="B45" s="47"/>
+      <c r="C45" s="48"/>
+      <c r="D45" s="48"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="50"/>
+      <c r="H45" s="50"/>
+      <c r="I45" s="59"/>
+      <c r="J45" s="60"/>
+      <c r="K45" s="59"/>
+      <c r="L45" s="54"/>
+      <c r="M45" s="54"/>
+      <c r="N45" s="54"/>
+      <c r="O45" s="54"/>
+      <c r="P45" s="54"/>
+      <c r="Q45" s="54"/>
+      <c r="R45" s="54"/>
+      <c r="S45" s="61"/>
+      <c r="T45" s="62"/>
+      <c r="U45" s="63"/>
+      <c r="V45" s="39"/>
     </row>
     <row r="46" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="45"/>
-      <c r="B46" s="46"/>
-      <c r="C46" s="47"/>
-      <c r="D46" s="47"/>
-      <c r="E46" s="48"/>
-      <c r="F46" s="48"/>
-      <c r="G46" s="49"/>
-      <c r="H46" s="49"/>
-      <c r="I46" s="58"/>
-      <c r="J46" s="59"/>
-      <c r="K46" s="58"/>
-      <c r="L46" s="53"/>
-      <c r="M46" s="53"/>
-      <c r="N46" s="53"/>
-      <c r="O46" s="53"/>
-      <c r="P46" s="53"/>
-      <c r="Q46" s="53"/>
-      <c r="R46" s="53"/>
-      <c r="S46" s="60"/>
-      <c r="T46" s="61"/>
-      <c r="U46" s="62"/>
-      <c r="V46" s="38"/>
+      <c r="A46" s="46"/>
+      <c r="B46" s="47"/>
+      <c r="C46" s="48"/>
+      <c r="D46" s="48"/>
+      <c r="E46" s="49"/>
+      <c r="F46" s="49"/>
+      <c r="G46" s="50"/>
+      <c r="H46" s="50"/>
+      <c r="I46" s="59"/>
+      <c r="J46" s="60"/>
+      <c r="K46" s="59"/>
+      <c r="L46" s="54"/>
+      <c r="M46" s="54"/>
+      <c r="N46" s="54"/>
+      <c r="O46" s="54"/>
+      <c r="P46" s="54"/>
+      <c r="Q46" s="54"/>
+      <c r="R46" s="54"/>
+      <c r="S46" s="61"/>
+      <c r="T46" s="62"/>
+      <c r="U46" s="63"/>
+      <c r="V46" s="39"/>
     </row>
     <row r="47" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="45"/>
-      <c r="B47" s="46"/>
-      <c r="C47" s="47"/>
-      <c r="D47" s="47"/>
-      <c r="E47" s="48"/>
-      <c r="F47" s="48"/>
-      <c r="G47" s="49"/>
-      <c r="H47" s="49"/>
-      <c r="I47" s="58"/>
-      <c r="J47" s="59"/>
-      <c r="K47" s="58"/>
-      <c r="L47" s="53"/>
-      <c r="M47" s="53"/>
-      <c r="N47" s="53"/>
-      <c r="O47" s="53"/>
-      <c r="P47" s="53"/>
-      <c r="Q47" s="53"/>
-      <c r="R47" s="53"/>
-      <c r="S47" s="60"/>
-      <c r="T47" s="61"/>
-      <c r="U47" s="62"/>
-      <c r="V47" s="38"/>
+      <c r="A47" s="46"/>
+      <c r="B47" s="47"/>
+      <c r="C47" s="48"/>
+      <c r="D47" s="48"/>
+      <c r="E47" s="49"/>
+      <c r="F47" s="49"/>
+      <c r="G47" s="50"/>
+      <c r="H47" s="50"/>
+      <c r="I47" s="59"/>
+      <c r="J47" s="60"/>
+      <c r="K47" s="59"/>
+      <c r="L47" s="54"/>
+      <c r="M47" s="54"/>
+      <c r="N47" s="54"/>
+      <c r="O47" s="54"/>
+      <c r="P47" s="54"/>
+      <c r="Q47" s="54"/>
+      <c r="R47" s="54"/>
+      <c r="S47" s="61"/>
+      <c r="T47" s="62"/>
+      <c r="U47" s="63"/>
+      <c r="V47" s="39"/>
     </row>
     <row r="48" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="45"/>
-      <c r="B48" s="46"/>
-      <c r="C48" s="47"/>
-      <c r="D48" s="47"/>
-      <c r="E48" s="48"/>
-      <c r="F48" s="48"/>
-      <c r="G48" s="49"/>
-      <c r="H48" s="49"/>
-      <c r="I48" s="58"/>
-      <c r="J48" s="59"/>
-      <c r="K48" s="58"/>
-      <c r="L48" s="53"/>
-      <c r="M48" s="53"/>
-      <c r="N48" s="53"/>
-      <c r="O48" s="53"/>
-      <c r="P48" s="53"/>
-      <c r="Q48" s="53"/>
-      <c r="R48" s="53"/>
-      <c r="S48" s="60"/>
-      <c r="T48" s="61"/>
-      <c r="U48" s="62"/>
-      <c r="V48" s="38"/>
+      <c r="A48" s="46"/>
+      <c r="B48" s="47"/>
+      <c r="C48" s="48"/>
+      <c r="D48" s="48"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="49"/>
+      <c r="G48" s="50"/>
+      <c r="H48" s="50"/>
+      <c r="I48" s="59"/>
+      <c r="J48" s="60"/>
+      <c r="K48" s="59"/>
+      <c r="L48" s="54"/>
+      <c r="M48" s="54"/>
+      <c r="N48" s="54"/>
+      <c r="O48" s="54"/>
+      <c r="P48" s="54"/>
+      <c r="Q48" s="54"/>
+      <c r="R48" s="54"/>
+      <c r="S48" s="61"/>
+      <c r="T48" s="62"/>
+      <c r="U48" s="63"/>
+      <c r="V48" s="39"/>
     </row>
     <row r="49" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="45"/>
-      <c r="B49" s="46"/>
-      <c r="C49" s="47"/>
-      <c r="D49" s="47"/>
-      <c r="E49" s="48"/>
-      <c r="F49" s="48"/>
-      <c r="G49" s="49"/>
-      <c r="H49" s="49"/>
-      <c r="I49" s="58"/>
-      <c r="J49" s="59"/>
-      <c r="K49" s="58"/>
-      <c r="L49" s="53"/>
-      <c r="M49" s="53"/>
-      <c r="N49" s="53"/>
-      <c r="O49" s="53"/>
-      <c r="P49" s="53"/>
-      <c r="Q49" s="53"/>
-      <c r="R49" s="53"/>
-      <c r="S49" s="60"/>
-      <c r="T49" s="61"/>
-      <c r="U49" s="62"/>
-      <c r="V49" s="38"/>
+      <c r="A49" s="46"/>
+      <c r="B49" s="47"/>
+      <c r="C49" s="48"/>
+      <c r="D49" s="48"/>
+      <c r="E49" s="49"/>
+      <c r="F49" s="49"/>
+      <c r="G49" s="50"/>
+      <c r="H49" s="50"/>
+      <c r="I49" s="59"/>
+      <c r="J49" s="60"/>
+      <c r="K49" s="59"/>
+      <c r="L49" s="54"/>
+      <c r="M49" s="54"/>
+      <c r="N49" s="54"/>
+      <c r="O49" s="54"/>
+      <c r="P49" s="54"/>
+      <c r="Q49" s="54"/>
+      <c r="R49" s="54"/>
+      <c r="S49" s="61"/>
+      <c r="T49" s="62"/>
+      <c r="U49" s="63"/>
+      <c r="V49" s="39"/>
     </row>
     <row r="50" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="45"/>
-      <c r="B50" s="46"/>
-      <c r="C50" s="47"/>
-      <c r="D50" s="47"/>
-      <c r="E50" s="48"/>
-      <c r="F50" s="48"/>
-      <c r="G50" s="49"/>
-      <c r="H50" s="49"/>
-      <c r="I50" s="58"/>
-      <c r="J50" s="59"/>
-      <c r="K50" s="58"/>
-      <c r="L50" s="53"/>
-      <c r="M50" s="53"/>
-      <c r="N50" s="53"/>
-      <c r="O50" s="53"/>
-      <c r="P50" s="53"/>
-      <c r="Q50" s="53"/>
-      <c r="R50" s="53"/>
-      <c r="S50" s="60"/>
-      <c r="T50" s="61"/>
-      <c r="U50" s="62"/>
-      <c r="V50" s="38"/>
+      <c r="A50" s="46"/>
+      <c r="B50" s="47"/>
+      <c r="C50" s="48"/>
+      <c r="D50" s="48"/>
+      <c r="E50" s="49"/>
+      <c r="F50" s="49"/>
+      <c r="G50" s="50"/>
+      <c r="H50" s="50"/>
+      <c r="I50" s="59"/>
+      <c r="J50" s="60"/>
+      <c r="K50" s="59"/>
+      <c r="L50" s="54"/>
+      <c r="M50" s="54"/>
+      <c r="N50" s="54"/>
+      <c r="O50" s="54"/>
+      <c r="P50" s="54"/>
+      <c r="Q50" s="54"/>
+      <c r="R50" s="54"/>
+      <c r="S50" s="61"/>
+      <c r="T50" s="62"/>
+      <c r="U50" s="63"/>
+      <c r="V50" s="39"/>
     </row>
     <row r="51" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="45"/>
-      <c r="B51" s="46"/>
-      <c r="C51" s="47"/>
-      <c r="D51" s="47"/>
-      <c r="E51" s="48"/>
-      <c r="F51" s="48"/>
-      <c r="G51" s="49"/>
-      <c r="H51" s="49"/>
-      <c r="I51" s="58"/>
-      <c r="J51" s="59"/>
-      <c r="K51" s="58"/>
-      <c r="L51" s="53"/>
-      <c r="M51" s="53"/>
-      <c r="N51" s="53"/>
-      <c r="O51" s="53"/>
-      <c r="P51" s="53"/>
-      <c r="Q51" s="53"/>
-      <c r="R51" s="53"/>
-      <c r="S51" s="60"/>
-      <c r="T51" s="61"/>
-      <c r="U51" s="62"/>
-      <c r="V51" s="38"/>
+      <c r="A51" s="46"/>
+      <c r="B51" s="47"/>
+      <c r="C51" s="48"/>
+      <c r="D51" s="48"/>
+      <c r="E51" s="49"/>
+      <c r="F51" s="49"/>
+      <c r="G51" s="50"/>
+      <c r="H51" s="50"/>
+      <c r="I51" s="59"/>
+      <c r="J51" s="60"/>
+      <c r="K51" s="59"/>
+      <c r="L51" s="54"/>
+      <c r="M51" s="54"/>
+      <c r="N51" s="54"/>
+      <c r="O51" s="54"/>
+      <c r="P51" s="54"/>
+      <c r="Q51" s="54"/>
+      <c r="R51" s="54"/>
+      <c r="S51" s="61"/>
+      <c r="T51" s="62"/>
+      <c r="U51" s="63"/>
+      <c r="V51" s="39"/>
     </row>
     <row r="52" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="45"/>
-      <c r="B52" s="46"/>
-      <c r="C52" s="47"/>
-      <c r="D52" s="47"/>
-      <c r="E52" s="48"/>
-      <c r="F52" s="48"/>
-      <c r="G52" s="49"/>
-      <c r="H52" s="49"/>
-      <c r="I52" s="58"/>
-      <c r="J52" s="59"/>
-      <c r="K52" s="58"/>
-      <c r="L52" s="53"/>
-      <c r="M52" s="53"/>
-      <c r="N52" s="53"/>
-      <c r="O52" s="53"/>
-      <c r="P52" s="53"/>
-      <c r="Q52" s="53"/>
-      <c r="R52" s="53"/>
-      <c r="S52" s="60"/>
-      <c r="T52" s="61"/>
-      <c r="U52" s="62"/>
-      <c r="V52" s="38"/>
+      <c r="A52" s="46"/>
+      <c r="B52" s="47"/>
+      <c r="C52" s="48"/>
+      <c r="D52" s="48"/>
+      <c r="E52" s="49"/>
+      <c r="F52" s="49"/>
+      <c r="G52" s="50"/>
+      <c r="H52" s="50"/>
+      <c r="I52" s="59"/>
+      <c r="J52" s="60"/>
+      <c r="K52" s="59"/>
+      <c r="L52" s="54"/>
+      <c r="M52" s="54"/>
+      <c r="N52" s="54"/>
+      <c r="O52" s="54"/>
+      <c r="P52" s="54"/>
+      <c r="Q52" s="54"/>
+      <c r="R52" s="54"/>
+      <c r="S52" s="61"/>
+      <c r="T52" s="62"/>
+      <c r="U52" s="63"/>
+      <c r="V52" s="39"/>
     </row>
     <row r="53" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="45"/>
-      <c r="B53" s="46"/>
-      <c r="C53" s="47"/>
-      <c r="D53" s="47"/>
-      <c r="E53" s="48"/>
-      <c r="F53" s="48"/>
-      <c r="G53" s="49"/>
-      <c r="H53" s="49"/>
-      <c r="I53" s="58"/>
-      <c r="J53" s="59"/>
-      <c r="K53" s="58"/>
-      <c r="L53" s="53"/>
-      <c r="M53" s="53"/>
-      <c r="N53" s="53"/>
-      <c r="O53" s="53"/>
-      <c r="P53" s="53"/>
-      <c r="Q53" s="53"/>
-      <c r="R53" s="53"/>
-      <c r="S53" s="60"/>
-      <c r="T53" s="61"/>
-      <c r="U53" s="62"/>
-      <c r="V53" s="38"/>
+      <c r="A53" s="46"/>
+      <c r="B53" s="47"/>
+      <c r="C53" s="48"/>
+      <c r="D53" s="48"/>
+      <c r="E53" s="49"/>
+      <c r="F53" s="49"/>
+      <c r="G53" s="50"/>
+      <c r="H53" s="50"/>
+      <c r="I53" s="59"/>
+      <c r="J53" s="60"/>
+      <c r="K53" s="59"/>
+      <c r="L53" s="54"/>
+      <c r="M53" s="54"/>
+      <c r="N53" s="54"/>
+      <c r="O53" s="54"/>
+      <c r="P53" s="54"/>
+      <c r="Q53" s="54"/>
+      <c r="R53" s="54"/>
+      <c r="S53" s="61"/>
+      <c r="T53" s="62"/>
+      <c r="U53" s="63"/>
+      <c r="V53" s="39"/>
     </row>
     <row r="54" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="45"/>
-      <c r="B54" s="46"/>
-      <c r="C54" s="47"/>
-      <c r="D54" s="47"/>
-      <c r="E54" s="48"/>
-      <c r="F54" s="48"/>
-      <c r="G54" s="49"/>
-      <c r="H54" s="49"/>
-      <c r="I54" s="58"/>
-      <c r="J54" s="59"/>
-      <c r="K54" s="58"/>
-      <c r="L54" s="53"/>
-      <c r="M54" s="53"/>
-      <c r="N54" s="53"/>
-      <c r="O54" s="53"/>
-      <c r="P54" s="53"/>
-      <c r="Q54" s="53"/>
-      <c r="R54" s="53"/>
-      <c r="S54" s="60"/>
-      <c r="T54" s="61"/>
-      <c r="U54" s="62"/>
-      <c r="V54" s="38"/>
+      <c r="A54" s="46"/>
+      <c r="B54" s="47"/>
+      <c r="C54" s="48"/>
+      <c r="D54" s="48"/>
+      <c r="E54" s="49"/>
+      <c r="F54" s="49"/>
+      <c r="G54" s="50"/>
+      <c r="H54" s="50"/>
+      <c r="I54" s="59"/>
+      <c r="J54" s="60"/>
+      <c r="K54" s="59"/>
+      <c r="L54" s="54"/>
+      <c r="M54" s="54"/>
+      <c r="N54" s="54"/>
+      <c r="O54" s="54"/>
+      <c r="P54" s="54"/>
+      <c r="Q54" s="54"/>
+      <c r="R54" s="54"/>
+      <c r="S54" s="61"/>
+      <c r="T54" s="62"/>
+      <c r="U54" s="63"/>
+      <c r="V54" s="39"/>
     </row>
     <row r="55" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="64"/>
-      <c r="B55" s="65"/>
-      <c r="C55" s="66"/>
-      <c r="D55" s="66"/>
-      <c r="E55" s="67"/>
-      <c r="F55" s="67"/>
-      <c r="G55" s="68"/>
-      <c r="H55" s="68"/>
-      <c r="I55" s="58"/>
-      <c r="J55" s="59"/>
-      <c r="K55" s="58"/>
-      <c r="L55" s="53"/>
-      <c r="M55" s="53"/>
-      <c r="N55" s="53"/>
-      <c r="O55" s="53"/>
-      <c r="P55" s="53"/>
-      <c r="Q55" s="53"/>
-      <c r="R55" s="53"/>
-      <c r="S55" s="60"/>
-      <c r="T55" s="61"/>
-      <c r="U55" s="62"/>
-      <c r="V55" s="38"/>
+      <c r="A55" s="65"/>
+      <c r="B55" s="66"/>
+      <c r="C55" s="67"/>
+      <c r="D55" s="67"/>
+      <c r="E55" s="68"/>
+      <c r="F55" s="68"/>
+      <c r="G55" s="69"/>
+      <c r="H55" s="69"/>
+      <c r="I55" s="59"/>
+      <c r="J55" s="60"/>
+      <c r="K55" s="59"/>
+      <c r="L55" s="54"/>
+      <c r="M55" s="54"/>
+      <c r="N55" s="54"/>
+      <c r="O55" s="54"/>
+      <c r="P55" s="54"/>
+      <c r="Q55" s="54"/>
+      <c r="R55" s="54"/>
+      <c r="S55" s="61"/>
+      <c r="T55" s="62"/>
+      <c r="U55" s="63"/>
+      <c r="V55" s="39"/>
     </row>
     <row r="56" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="69"/>
-      <c r="B56" s="70"/>
-      <c r="C56" s="71"/>
-      <c r="D56" s="71"/>
-      <c r="E56" s="72"/>
-      <c r="F56" s="72"/>
-      <c r="G56" s="63"/>
-      <c r="H56" s="63"/>
-      <c r="I56" s="58"/>
-      <c r="J56" s="59"/>
-      <c r="K56" s="58"/>
-      <c r="L56" s="53"/>
-      <c r="M56" s="53"/>
-      <c r="N56" s="53"/>
-      <c r="O56" s="53"/>
-      <c r="P56" s="53"/>
-      <c r="Q56" s="53"/>
-      <c r="R56" s="53"/>
-      <c r="S56" s="60"/>
-      <c r="T56" s="61"/>
-      <c r="U56" s="62"/>
-      <c r="V56" s="38"/>
+      <c r="A56" s="70"/>
+      <c r="B56" s="71"/>
+      <c r="C56" s="72"/>
+      <c r="D56" s="72"/>
+      <c r="E56" s="73"/>
+      <c r="F56" s="73"/>
+      <c r="G56" s="64"/>
+      <c r="H56" s="64"/>
+      <c r="I56" s="59"/>
+      <c r="J56" s="60"/>
+      <c r="K56" s="59"/>
+      <c r="L56" s="54"/>
+      <c r="M56" s="54"/>
+      <c r="N56" s="54"/>
+      <c r="O56" s="54"/>
+      <c r="P56" s="54"/>
+      <c r="Q56" s="54"/>
+      <c r="R56" s="54"/>
+      <c r="S56" s="61"/>
+      <c r="T56" s="62"/>
+      <c r="U56" s="63"/>
+      <c r="V56" s="39"/>
     </row>
     <row r="57" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="45"/>
-      <c r="B57" s="46"/>
-      <c r="C57" s="47"/>
-      <c r="D57" s="47"/>
-      <c r="E57" s="48"/>
-      <c r="F57" s="48"/>
-      <c r="G57" s="49"/>
-      <c r="H57" s="49"/>
-      <c r="I57" s="58"/>
-      <c r="J57" s="59"/>
-      <c r="K57" s="58"/>
-      <c r="L57" s="53"/>
-      <c r="M57" s="53"/>
-      <c r="N57" s="53"/>
-      <c r="O57" s="53"/>
-      <c r="P57" s="53"/>
-      <c r="Q57" s="53"/>
-      <c r="R57" s="53"/>
-      <c r="S57" s="60"/>
-      <c r="T57" s="61"/>
-      <c r="U57" s="62"/>
-      <c r="V57" s="38"/>
+      <c r="A57" s="46"/>
+      <c r="B57" s="47"/>
+      <c r="C57" s="48"/>
+      <c r="D57" s="48"/>
+      <c r="E57" s="49"/>
+      <c r="F57" s="49"/>
+      <c r="G57" s="50"/>
+      <c r="H57" s="50"/>
+      <c r="I57" s="59"/>
+      <c r="J57" s="60"/>
+      <c r="K57" s="59"/>
+      <c r="L57" s="54"/>
+      <c r="M57" s="54"/>
+      <c r="N57" s="54"/>
+      <c r="O57" s="54"/>
+      <c r="P57" s="54"/>
+      <c r="Q57" s="54"/>
+      <c r="R57" s="54"/>
+      <c r="S57" s="61"/>
+      <c r="T57" s="62"/>
+      <c r="U57" s="63"/>
+      <c r="V57" s="39"/>
     </row>
     <row r="58" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="64"/>
-      <c r="B58" s="65"/>
-      <c r="C58" s="66"/>
-      <c r="D58" s="66"/>
-      <c r="E58" s="67"/>
-      <c r="F58" s="67"/>
-      <c r="G58" s="68"/>
-      <c r="H58" s="68"/>
-      <c r="I58" s="73"/>
-      <c r="J58" s="74"/>
-      <c r="K58" s="73"/>
-      <c r="L58" s="53"/>
-      <c r="M58" s="53"/>
-      <c r="N58" s="53"/>
-      <c r="O58" s="53"/>
-      <c r="P58" s="75"/>
-      <c r="Q58" s="53"/>
-      <c r="R58" s="53"/>
-      <c r="S58" s="76"/>
-      <c r="T58" s="77"/>
-      <c r="U58" s="78"/>
-      <c r="V58" s="38"/>
+      <c r="A58" s="65"/>
+      <c r="B58" s="66"/>
+      <c r="C58" s="67"/>
+      <c r="D58" s="67"/>
+      <c r="E58" s="68"/>
+      <c r="F58" s="68"/>
+      <c r="G58" s="69"/>
+      <c r="H58" s="69"/>
+      <c r="I58" s="74"/>
+      <c r="J58" s="75"/>
+      <c r="K58" s="74"/>
+      <c r="L58" s="54"/>
+      <c r="M58" s="54"/>
+      <c r="N58" s="54"/>
+      <c r="O58" s="54"/>
+      <c r="P58" s="76"/>
+      <c r="Q58" s="54"/>
+      <c r="R58" s="54"/>
+      <c r="S58" s="77"/>
+      <c r="T58" s="78"/>
+      <c r="U58" s="79"/>
+      <c r="V58" s="39"/>
     </row>
     <row r="59" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="79"/>
-      <c r="B59" s="79"/>
-      <c r="C59" s="79"/>
-      <c r="D59" s="79"/>
-      <c r="E59" s="79"/>
-      <c r="F59" s="79"/>
-      <c r="G59" s="79"/>
-      <c r="H59" s="79"/>
-      <c r="I59" s="79"/>
-      <c r="J59" s="79"/>
-      <c r="K59" s="79"/>
-      <c r="L59" s="79"/>
-      <c r="M59" s="79"/>
-      <c r="N59" s="79"/>
-      <c r="O59" s="79"/>
-      <c r="P59" s="79"/>
-      <c r="Q59" s="79"/>
-      <c r="R59" s="79"/>
-      <c r="S59" s="79"/>
-      <c r="T59" s="79"/>
-      <c r="U59" s="80"/>
-      <c r="V59" s="38"/>
+      <c r="A59" s="80"/>
+      <c r="B59" s="80"/>
+      <c r="C59" s="80"/>
+      <c r="D59" s="80"/>
+      <c r="E59" s="80"/>
+      <c r="F59" s="80"/>
+      <c r="G59" s="80"/>
+      <c r="H59" s="80"/>
+      <c r="I59" s="80"/>
+      <c r="J59" s="80"/>
+      <c r="K59" s="80"/>
+      <c r="L59" s="80"/>
+      <c r="M59" s="80"/>
+      <c r="N59" s="80"/>
+      <c r="O59" s="80"/>
+      <c r="P59" s="80"/>
+      <c r="Q59" s="80"/>
+      <c r="R59" s="80"/>
+      <c r="S59" s="80"/>
+      <c r="T59" s="80"/>
+      <c r="U59" s="81"/>
+      <c r="V59" s="39"/>
     </row>
     <row r="60" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="17"/>
@@ -4596,11 +4600,11 @@
       <c r="D60" s="18"/>
       <c r="E60" s="18"/>
       <c r="F60" s="18"/>
-      <c r="G60" s="81"/>
-      <c r="H60" s="82"/>
-      <c r="I60" s="82"/>
-      <c r="J60" s="82"/>
-      <c r="K60" s="82"/>
+      <c r="G60" s="82"/>
+      <c r="H60" s="83"/>
+      <c r="I60" s="83"/>
+      <c r="J60" s="83"/>
+      <c r="K60" s="83"/>
       <c r="L60" s="23"/>
       <c r="M60" s="23"/>
       <c r="N60" s="23"/>
@@ -4611,7 +4615,7 @@
       <c r="S60" s="23"/>
       <c r="T60" s="23"/>
       <c r="U60" s="23"/>
-      <c r="V60" s="38"/>
+      <c r="V60" s="39"/>
     </row>
     <row r="61" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="20"/>
@@ -4620,22 +4624,22 @@
       <c r="D61" s="18"/>
       <c r="E61" s="18"/>
       <c r="F61" s="18"/>
-      <c r="G61" s="81"/>
-      <c r="H61" s="82"/>
-      <c r="I61" s="82"/>
-      <c r="J61" s="82"/>
-      <c r="K61" s="82"/>
-      <c r="L61" s="83"/>
-      <c r="M61" s="84"/>
-      <c r="N61" s="84"/>
-      <c r="O61" s="84"/>
-      <c r="P61" s="84"/>
-      <c r="Q61" s="84"/>
-      <c r="R61" s="84"/>
-      <c r="S61" s="83"/>
-      <c r="T61" s="83"/>
-      <c r="U61" s="84"/>
-      <c r="V61" s="38"/>
+      <c r="G61" s="82"/>
+      <c r="H61" s="83"/>
+      <c r="I61" s="83"/>
+      <c r="J61" s="83"/>
+      <c r="K61" s="83"/>
+      <c r="L61" s="84"/>
+      <c r="M61" s="85"/>
+      <c r="N61" s="85"/>
+      <c r="O61" s="85"/>
+      <c r="P61" s="85"/>
+      <c r="Q61" s="85"/>
+      <c r="R61" s="85"/>
+      <c r="S61" s="84"/>
+      <c r="T61" s="84"/>
+      <c r="U61" s="85"/>
+      <c r="V61" s="39"/>
     </row>
     <row r="62" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="20"/>
@@ -4644,22 +4648,22 @@
       <c r="D62" s="21"/>
       <c r="E62" s="18"/>
       <c r="F62" s="18"/>
-      <c r="G62" s="85"/>
-      <c r="H62" s="85"/>
+      <c r="G62" s="86"/>
+      <c r="H62" s="86"/>
       <c r="I62" s="23"/>
       <c r="J62" s="23"/>
-      <c r="K62" s="83"/>
-      <c r="L62" s="86"/>
+      <c r="K62" s="84"/>
+      <c r="L62" s="87"/>
       <c r="M62" s="20"/>
-      <c r="N62" s="84"/>
+      <c r="N62" s="85"/>
       <c r="O62" s="21"/>
       <c r="P62" s="20"/>
-      <c r="Q62" s="84"/>
-      <c r="R62" s="84"/>
-      <c r="S62" s="83"/>
-      <c r="T62" s="83"/>
-      <c r="U62" s="84"/>
-      <c r="V62" s="38"/>
+      <c r="Q62" s="85"/>
+      <c r="R62" s="85"/>
+      <c r="S62" s="84"/>
+      <c r="T62" s="84"/>
+      <c r="U62" s="85"/>
+      <c r="V62" s="39"/>
     </row>
     <row r="63" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="22"/>
@@ -4671,19 +4675,19 @@
       <c r="G63" s="22"/>
       <c r="H63" s="22"/>
       <c r="I63" s="22"/>
-      <c r="J63" s="87"/>
-      <c r="K63" s="87"/>
+      <c r="J63" s="88"/>
+      <c r="K63" s="88"/>
       <c r="L63" s="22"/>
-      <c r="M63" s="88"/>
+      <c r="M63" s="89"/>
       <c r="N63" s="22"/>
-      <c r="O63" s="88"/>
-      <c r="P63" s="88"/>
-      <c r="Q63" s="88"/>
-      <c r="R63" s="88"/>
-      <c r="S63" s="88"/>
-      <c r="T63" s="88"/>
-      <c r="U63" s="88"/>
-      <c r="V63" s="38"/>
+      <c r="O63" s="89"/>
+      <c r="P63" s="89"/>
+      <c r="Q63" s="89"/>
+      <c r="R63" s="89"/>
+      <c r="S63" s="89"/>
+      <c r="T63" s="89"/>
+      <c r="U63" s="89"/>
+      <c r="V63" s="39"/>
     </row>
     <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="24"/>
@@ -4707,7 +4711,7 @@
       <c r="S64" s="28"/>
       <c r="T64" s="30"/>
       <c r="U64" s="31"/>
-      <c r="V64" s="38"/>
+      <c r="V64" s="39"/>
     </row>
     <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="26"/>
@@ -4731,7 +4735,7 @@
       <c r="S65" s="25"/>
       <c r="T65" s="25"/>
       <c r="U65" s="31"/>
-      <c r="V65" s="38"/>
+      <c r="V65" s="39"/>
     </row>
     <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="28"/>
@@ -4753,9 +4757,9 @@
       <c r="Q66" s="23"/>
       <c r="R66" s="24"/>
       <c r="S66" s="24"/>
-      <c r="T66" s="89"/>
+      <c r="T66" s="90"/>
       <c r="U66" s="31"/>
-      <c r="V66" s="38"/>
+      <c r="V66" s="39"/>
     </row>
     <row r="67" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="26"/>
@@ -4765,7 +4769,7 @@
       <c r="E67" s="25"/>
       <c r="F67" s="25"/>
       <c r="G67" s="25"/>
-      <c r="H67" s="83"/>
+      <c r="H67" s="84"/>
       <c r="I67" s="25"/>
       <c r="J67" s="25"/>
       <c r="K67" s="25"/>
@@ -4779,7 +4783,7 @@
       <c r="S67" s="25"/>
       <c r="T67" s="25"/>
       <c r="U67" s="31"/>
-      <c r="V67" s="38"/>
+      <c r="V67" s="39"/>
     </row>
     <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="29"/>
@@ -4803,7 +4807,7 @@
       <c r="S68" s="28"/>
       <c r="T68" s="30"/>
       <c r="U68" s="31"/>
-      <c r="V68" s="38"/>
+      <c r="V68" s="39"/>
     </row>
     <row r="69" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="26"/>
@@ -4827,7 +4831,7 @@
       <c r="S69" s="29"/>
       <c r="T69" s="29"/>
       <c r="U69" s="8"/>
-      <c r="V69" s="38"/>
+      <c r="V69" s="39"/>
     </row>
     <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="29"/>
@@ -4839,8 +4843,8 @@
       <c r="G70" s="28"/>
       <c r="H70" s="28"/>
       <c r="I70" s="25"/>
-      <c r="J70" s="90"/>
-      <c r="K70" s="90"/>
+      <c r="J70" s="91"/>
+      <c r="K70" s="91"/>
       <c r="L70" s="24"/>
       <c r="M70" s="24"/>
       <c r="N70" s="25"/>
@@ -4849,9 +4853,9 @@
       <c r="Q70" s="23"/>
       <c r="R70" s="24"/>
       <c r="S70" s="24"/>
-      <c r="T70" s="89"/>
+      <c r="T70" s="90"/>
       <c r="U70" s="31"/>
-      <c r="V70" s="38"/>
+      <c r="V70" s="39"/>
     </row>
     <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="32"/>
@@ -4875,7 +4879,7 @@
       <c r="S71" s="31"/>
       <c r="T71" s="31"/>
       <c r="U71" s="8"/>
-      <c r="V71" s="38"/>
+      <c r="V71" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="23">

--- a/outputs/54667.xlsx
+++ b/outputs/54667.xlsx
@@ -1419,9 +1419,9 @@
         <f aca="true">IF(OR(B3="PRG/FLY",B3="PRG/TVL",B3="FLY1",B3="TVL1",B3="PRG/FLY-CO",B3="PRG/TVL-CO",B3="FLY1-CO",B3="TVL1-CO"),IF(IFERROR(1/(1/F3),"")="",TODAY()+VLOOKUP(C3,DATA!$A:$E,4,0),F3),"")</f>
         <v>46271.3645833333</v>
       </c>
-      <c r="G3" s="4" t="n">
-        <f aca="false">IF(D3=E3,M3,IFERROR(VLOOKUP(C3,DATA!$A:$E,5,0),""))</f>
-        <v>0.0520833333333333</v>
+      <c r="G3" s="4" t="str">
+        <f aca="false">IF(E3=D3,M3,"")</f>
+        <v/>
       </c>
       <c r="M3" s="4" t="n">
         <v>0.0541666666666667</v>
@@ -1447,9 +1447,9 @@
         <f aca="true">IF(OR(B4="PRG/FLY",B4="PRG/TVL",B4="FLY1",B4="TVL1",B4="PRG/FLY-CO",B4="PRG/TVL-CO",B4="FLY1-CO",B4="TVL1-CO"),IF(IFERROR(1/(1/F4),"")="",TODAY()+VLOOKUP(C4,DATA!$A:$E,4,0),F4),"")</f>
         <v/>
       </c>
-      <c r="G4" s="4" t="n">
-        <f aca="false">IF(D4=E4,M4,IFERROR(VLOOKUP(C4,DATA!$A:$E,5,0),""))</f>
-        <v>0.0381944444444445</v>
+      <c r="G4" s="4" t="str">
+        <f aca="false">IF(E4=D4,M4,"")</f>
+        <v/>
       </c>
       <c r="M4" s="4" t="n">
         <v>0.0409722222222222</v>
@@ -1475,7 +1475,7 @@
         <v/>
       </c>
       <c r="G5" s="15" t="n">
-        <f aca="false">IF(D5=E5,M5,IFERROR(VLOOKUP(C5,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E5=D5,M5,"")</f>
         <v>0.05625</v>
       </c>
       <c r="M5" s="15" t="n">
@@ -1499,7 +1499,7 @@
         <v/>
       </c>
       <c r="G6" s="4" t="n">
-        <f aca="false">IF(D6=E6,M6,IFERROR(VLOOKUP(C6,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E6=D6,M6,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
         <v/>
       </c>
       <c r="G7" s="4" t="n">
-        <f aca="false">IF(D7=E7,M7,IFERROR(VLOOKUP(C7,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E7=D7,M7,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
         <v/>
       </c>
       <c r="G8" s="4" t="n">
-        <f aca="false">IF(D8=E8,M8,IFERROR(VLOOKUP(C8,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E8=D8,M8,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
         <v/>
       </c>
       <c r="G9" s="4" t="n">
-        <f aca="false">IF(D9=E9,M9,IFERROR(VLOOKUP(C9,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E9=D9,M9,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
         <v/>
       </c>
       <c r="G10" s="4" t="n">
-        <f aca="false">IF(D10=E10,M10,IFERROR(VLOOKUP(C10,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E10=D10,M10,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
         <v/>
       </c>
       <c r="G11" s="4" t="n">
-        <f aca="false">IF(D11=E11,M11,IFERROR(VLOOKUP(C11,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E11=D11,M11,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
         <v/>
       </c>
       <c r="G12" s="4" t="n">
-        <f aca="false">IF(D12=E12,M12,IFERROR(VLOOKUP(C12,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E12=D12,M12,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
         <v/>
       </c>
       <c r="G13" s="4" t="n">
-        <f aca="false">IF(D13=E13,M13,IFERROR(VLOOKUP(C13,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E13=D13,M13,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="G14" s="4" t="n">
-        <f aca="false">IF(D14=E14,M14,IFERROR(VLOOKUP(C14,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E14=D14,M14,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1688,7 +1688,7 @@
         <v/>
       </c>
       <c r="G15" s="4" t="n">
-        <f aca="false">IF(D15=E15,M15,IFERROR(VLOOKUP(C15,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E15=D15,M15,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
         <v/>
       </c>
       <c r="G16" s="4" t="n">
-        <f aca="false">IF(D16=E16,M16,IFERROR(VLOOKUP(C16,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E16=D16,M16,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v/>
       </c>
       <c r="G17" s="4" t="n">
-        <f aca="false">IF(D17=E17,M17,IFERROR(VLOOKUP(C17,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E17=D17,M17,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
         <v/>
       </c>
       <c r="G18" s="4" t="n">
-        <f aca="false">IF(D18=E18,M18,IFERROR(VLOOKUP(C18,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E18=D18,M18,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1772,7 +1772,7 @@
         <v/>
       </c>
       <c r="G19" s="4" t="n">
-        <f aca="false">IF(D19=E19,M19,IFERROR(VLOOKUP(C19,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E19=D19,M19,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
         <v/>
       </c>
       <c r="G20" s="4" t="n">
-        <f aca="false">IF(D20=E20,M20,IFERROR(VLOOKUP(C20,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E20=D20,M20,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1814,7 +1814,7 @@
         <v/>
       </c>
       <c r="G21" s="4" t="n">
-        <f aca="false">IF(D21=E21,M21,IFERROR(VLOOKUP(C21,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E21=D21,M21,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
         <v/>
       </c>
       <c r="G22" s="4" t="n">
-        <f aca="false">IF(D22=E22,M22,IFERROR(VLOOKUP(C22,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E22=D22,M22,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
         <v/>
       </c>
       <c r="G23" s="4" t="n">
-        <f aca="false">IF(D23=E23,M23,IFERROR(VLOOKUP(C23,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E23=D23,M23,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
         <v/>
       </c>
       <c r="G24" s="4" t="n">
-        <f aca="false">IF(D24=E24,M24,IFERROR(VLOOKUP(C24,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E24=D24,M24,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
         <v/>
       </c>
       <c r="G25" s="4" t="n">
-        <f aca="false">IF(D25=E25,M25,IFERROR(VLOOKUP(C25,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E25=D25,M25,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
         <v/>
       </c>
       <c r="G26" s="4" t="n">
-        <f aca="false">IF(D26=E26,M26,IFERROR(VLOOKUP(C26,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E26=D26,M26,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
         <v/>
       </c>
       <c r="G27" s="4" t="n">
-        <f aca="false">IF(D27=E27,M27,IFERROR(VLOOKUP(C27,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E27=D27,M27,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
         <v/>
       </c>
       <c r="G28" s="4" t="n">
-        <f aca="false">IF(D28=E28,M28,IFERROR(VLOOKUP(C28,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E28=D28,M28,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         <v/>
       </c>
       <c r="G29" s="4" t="n">
-        <f aca="false">IF(D29=E29,M29,IFERROR(VLOOKUP(C29,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E29=D29,M29,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2003,7 +2003,7 @@
         <v/>
       </c>
       <c r="G30" s="4" t="n">
-        <f aca="false">IF(D30=E30,M30,IFERROR(VLOOKUP(C30,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E30=D30,M30,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
         <v/>
       </c>
       <c r="G31" s="4" t="n">
-        <f aca="false">IF(D31=E31,M31,IFERROR(VLOOKUP(C31,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E31=D31,M31,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2045,7 +2045,7 @@
         <v/>
       </c>
       <c r="G32" s="4" t="n">
-        <f aca="false">IF(D32=E32,M32,IFERROR(VLOOKUP(C32,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E32=D32,M32,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
         <v/>
       </c>
       <c r="G33" s="4" t="n">
-        <f aca="false">IF(D33=E33,M33,IFERROR(VLOOKUP(C33,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E33=D33,M33,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
         <v/>
       </c>
       <c r="G34" s="4" t="n">
-        <f aca="false">IF(D34=E34,M34,IFERROR(VLOOKUP(C34,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E34=D34,M34,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
         <v/>
       </c>
       <c r="G35" s="4" t="n">
-        <f aca="false">IF(D35=E35,M35,IFERROR(VLOOKUP(C35,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E35=D35,M35,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2129,7 +2129,7 @@
         <v/>
       </c>
       <c r="G36" s="4" t="n">
-        <f aca="false">IF(D36=E36,M36,IFERROR(VLOOKUP(C36,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E36=D36,M36,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
         <v/>
       </c>
       <c r="G37" s="4" t="n">
-        <f aca="false">IF(D37=E37,M37,IFERROR(VLOOKUP(C37,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E37=D37,M37,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         <v/>
       </c>
       <c r="G38" s="4" t="n">
-        <f aca="false">IF(D38=E38,M38,IFERROR(VLOOKUP(C38,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E38=D38,M38,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
         <v/>
       </c>
       <c r="G39" s="4" t="n">
-        <f aca="false">IF(D39=E39,M39,IFERROR(VLOOKUP(C39,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E39=D39,M39,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2213,7 +2213,7 @@
         <v/>
       </c>
       <c r="G40" s="4" t="n">
-        <f aca="false">IF(D40=E40,M40,IFERROR(VLOOKUP(C40,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E40=D40,M40,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
         <v/>
       </c>
       <c r="G41" s="4" t="n">
-        <f aca="false">IF(D41=E41,M41,IFERROR(VLOOKUP(C41,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E41=D41,M41,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2255,7 +2255,7 @@
         <v/>
       </c>
       <c r="G42" s="4" t="n">
-        <f aca="false">IF(D42=E42,M42,IFERROR(VLOOKUP(C42,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E42=D42,M42,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
         <v/>
       </c>
       <c r="G43" s="4" t="n">
-        <f aca="false">IF(D43=E43,M43,IFERROR(VLOOKUP(C43,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E43=D43,M43,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
         <v/>
       </c>
       <c r="G44" s="4" t="n">
-        <f aca="false">IF(D44=E44,M44,IFERROR(VLOOKUP(C44,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E44=D44,M44,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
         <v/>
       </c>
       <c r="G45" s="4" t="n">
-        <f aca="false">IF(D45=E45,M45,IFERROR(VLOOKUP(C45,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E45=D45,M45,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v/>
       </c>
       <c r="G46" s="4" t="n">
-        <f aca="false">IF(D46=E46,M46,IFERROR(VLOOKUP(C46,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E46=D46,M46,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
         <v/>
       </c>
       <c r="G47" s="4" t="n">
-        <f aca="false">IF(D47=E47,M47,IFERROR(VLOOKUP(C47,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E47=D47,M47,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         <v/>
       </c>
       <c r="G48" s="4" t="n">
-        <f aca="false">IF(D48=E48,M48,IFERROR(VLOOKUP(C48,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E48=D48,M48,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
         <v/>
       </c>
       <c r="G49" s="4" t="n">
-        <f aca="false">IF(D49=E49,M49,IFERROR(VLOOKUP(C49,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E49=D49,M49,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2423,7 +2423,7 @@
         <v/>
       </c>
       <c r="G50" s="4" t="n">
-        <f aca="false">IF(D50=E50,M50,IFERROR(VLOOKUP(C50,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E50=D50,M50,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
         <v/>
       </c>
       <c r="G51" s="4" t="n">
-        <f aca="false">IF(D51=E51,M51,IFERROR(VLOOKUP(C51,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E51=D51,M51,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="G52" s="4" t="n">
-        <f aca="false">IF(D52=E52,M52,IFERROR(VLOOKUP(C52,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E52=D52,M52,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
         <v/>
       </c>
       <c r="G53" s="4" t="n">
-        <f aca="false">IF(D53=E53,M53,IFERROR(VLOOKUP(C53,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E53=D53,M53,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2507,7 +2507,7 @@
         <v/>
       </c>
       <c r="G54" s="4" t="n">
-        <f aca="false">IF(D54=E54,M54,IFERROR(VLOOKUP(C54,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E54=D54,M54,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
         <v/>
       </c>
       <c r="G55" s="4" t="n">
-        <f aca="false">IF(D55=E55,M55,IFERROR(VLOOKUP(C55,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E55=D55,M55,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
         <v/>
       </c>
       <c r="G56" s="4" t="n">
-        <f aca="false">IF(D56=E56,M56,IFERROR(VLOOKUP(C56,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E56=D56,M56,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2570,7 +2570,7 @@
         <v/>
       </c>
       <c r="G57" s="4" t="n">
-        <f aca="false">IF(D57=E57,M57,IFERROR(VLOOKUP(C57,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E57=D57,M57,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
         <v/>
       </c>
       <c r="G58" s="4" t="n">
-        <f aca="false">IF(D58=E58,M58,IFERROR(VLOOKUP(C58,DATA!$A:$E,5,0),""))</f>
+        <f aca="false">IF(E58=D58,M58,"")</f>
         <v>0</v>
       </c>
     </row>
